--- a/avaliacoes/avaliacoes_completas.xlsx
+++ b/avaliacoes/avaliacoes_completas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="106">
   <si>
     <t>Total de Experimentos</t>
   </si>
@@ -72,7 +72,7 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 - Gerenciamento de Projetos e Squads:** O sistema deve permitir a criação, edição e visualização de projetos, possibilitando a associação de clientes, definição de escopo, status do projeto e a alocação de membros da EJCM aos respectivos squads de desenvolvimento.
+*   **RF01 - Gerenciamento de Projetos e Squads:** O sistema deve permitir a criação, edição e visualização de projetos, possibilitando a associação de clientes, definição de escopo, status do projeto e a alocação de membros da &lt;Empresa Júnior&gt; aos respectivos squads de desenvolvimento.
 *   **RF02 - Planejamento e Controle de Sprints:** O sistema deve permitir que o Gerente de Projetos crie e configure Sprints, definindo datas de início e fim, metas da sprint e associando as tarefas que farão parte do período planejado.
 *   **RF03 - Quadro Kanban de Tarefas:** O sistema deve disponibilizar um painel visual (Kanban) para o acompanhamento do fluxo de trabalho das tarefas, permitindo a transição de status (ex: Backlog, Em Desenvolvimento, Teste/Validação, Concluído) por meio de arrastar e soltar (drag-and-drop).
 *   **RF04 - Detalhamento e Atribuição de Tarefas:** O sistema deve permitir a criação de tarefas detalhadas, contendo título, descrição enriquecida, responsáveis, prazos de entrega (deadlines), etiquetas de categorização (tags) e nível de prioridade.
@@ -104,7 +104,7 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 - Centralização de Projetos:** O sistema deve permitir criar, editar, visualizar e arquivar projetos, categorizando-os de acordo com as etapas do ciclo de vida da EJCM (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
+*   **RF01 - Centralização de Projetos:** O sistema deve permitir criar, editar, visualizar e arquivar projetos, categorizando-os de acordo com as etapas do ciclo de vida da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
 *   **RF02 - Planejamento de Sprints:** O sistema deve permitir que o Gerente de Projetos crie e configure sprints, definindo metas, data de início, data de término e associando as tarefas correspondentes.
 *   **RF03 - Quadro Kanban:** O sistema deve fornecer uma visualização de tarefas em formato Kanban, permitindo a movimentação de cartões entre colunas customizáveis (ex: A Fazer, Em Desenvolvimento, Revisão, Concluído).
 *   **RF04 - Atribuição de Tarefas:** O sistema deve permitir associar tarefas a um ou mais membros do squad do projeto, definindo prazos de entrega, nível de prioridade e descrição da demanda.
@@ -130,11 +130,11 @@
   </si>
   <si>
     <t>### Requisitos Funcionais (RF)
-* **RF01 - Gerenciamento do Ciclo de Vida do Projeto:** O sistema deve permitir o cadastro, monitoramento e controle das etapas do ciclo de vida dos projetos da EJCM (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
+* **RF01 - Gerenciamento do Ciclo de Vida do Projeto:** O sistema deve permitir o cadastro, monitoramento e controle das etapas do ciclo de vida dos projetos da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
 * **RF02 - Painel de Controle Unificado (Dashboard):** O sistema deve disponibilizar um dashboard centralizado que apresente o status do projeto, cronograma, distribuição de tarefas e indicadores de produtividade do squad em tempo real.
 * **RF03 - Planejamento e Acompanhamento de Sprints:** O sistema deve permitir a criação e o gerenciamento de sprints, possibilitando definir metas, prazos, estimativas de esforço e associação de tarefas.
 * **RF04 - Quadro Kanban de Tarefas:** O sistema deve fornecer um quadro visual interativo (estilo Kanban) para a criação, atribuição, categorização e movimentação de tarefas entre os membros do squad.
-* **RF05 - Gestão de Squads:** O sistema deve permitir a alocação de membros da EJCM em squads específicos de projetos, com a definição de seus respectivos papéis e responsabilidades no fluxo de trabalho.
+* **RF05 - Gestão de Squads:** O sistema deve permitir a alocação de membros da &lt;Empresa Júnior&gt; em squads específicos de projetos, com a definição de seus respectivos papéis e responsabilidades no fluxo de trabalho.
 * **RF06 - Registro de Horas (Time Tracking):** O sistema deve possuir uma funcionalidade para que os membros do squad registrem as horas trabalhadas em cada tarefa, permitindo ao Gerente de Projetos extrair relatórios de produtividade.
 * **RF07 - Central de Documentação e Repositório:** O sistema deve permitir a criação, edição e armazenamento de documentos de texto diretamente na plataforma, utilizando templates padronizados para cada fase do projeto.
 * **RF08 - Registro de Atas de Reunião:** O sistema deve possuir um módulo para o registro e armazenamento de atas de reuniões, permitindo associar participantes, pautas discutidas e planos de ação ao projeto.
@@ -147,7 +147,7 @@
 * **RNF02 - Compatibilidade Multiplataforma:** O sistema deve ser acessível via navegadores web modernos e ser totalmente funcional em computadores pessoais, corporativos e dispositivos institucionais.
 * **RNF03 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a informações e funcionalidades com base no perfil do usuário (ex: Gerente de Projetos, Membro do Squad, Cliente), garantindo a segurança dos dados.
 * **RNF04 - Desempenho na Busca:** O mecanismo de busca global do sistema deve retornar resultados em um tempo máximo de 2 segundos, mesmo em uma base de dados com alto volume de documentos históricos.
-* **RNF05 - Disponibilidade:** O sistema deve apresentar uma taxa de disponibilidade (uptime) mínima de 99,5% durante os dias úteis, garantindo o suporte às operações diárias da EJCM.
+* **RNF05 - Disponibilidade:** O sistema deve apresentar uma taxa de disponibilidade (uptime) mínima de 99,5% durante os dias úteis, garantindo o suporte às operações diárias da &lt;Empresa Júnior&gt;.
 * **RNF06 - Segurança e Compartilhamento de Dados:** O sistema deve garantir que o compartilhamento de documentos e informações estratégicas seja feito de forma segura, permitindo a definição de permissões de leitura e escrita por usuário ou squad.</t>
   </si>
   <si>
@@ -188,11 +188,11 @@
 *   **RF02 - Gestão de Sprints e Backlog:** O sistema deve permitir que o Gerente de Projetos crie, planeje e gerencie sprints, incluindo a criação de um backlog de produto, estimativa de esforço, priorização de demandas e acompanhamento visual do progresso por meio de um quadro Kanban.
 *   **RF03 - Distribuição e Acompanhamento de Tarefas:** O sistema deve permitir a criação de tarefas, atribuição de responsáveis (membros do squad), definição de prazos, níveis de prioridade e checklist de subtarefas.
 *   **RF04 - Registro de Tempo de Execução (Timesheet):** O sistema deve possuir uma funcionalidade integrada para registrar o tempo gasto pelos membros do squad em cada tarefa (equivalente ao Clockify), permitindo a extração de relatórios de produtividade.
-*   **RF05 - Alocação e Gestão de Squads:** O sistema deve permitir ao Gerente de Projetos alocar membros da EJCM a squads específicos de projetos, definindo seus papéis (Ex: Desenvolvedor, Designer, Líder Técnico).
+*   **RF05 - Alocação e Gestão de Squads:** O sistema deve permitir ao Gerente de Projetos alocar membros da &lt;Empresa Júnior&gt; a squads específicos de projetos, definindo seus papéis (Ex: Desenvolvedor, Designer, Líder Técnico).
 *   **RF06 - Repositório de Documentos e Gestão do Conhecimento:** O sistema deve permitir o upload, organização em pastas e edição de documentos do projeto (pesquisas de UX, especificações, protótipos e manuais de suporte), com suporte a controle de versão para evitar perda de histórico.
 *   **RF07 - Registro de Reuniões e Atas:** O sistema deve disponibilizar um módulo para agendamento de reuniões e preenchimento de atas (atas de reunião), associando-as diretamente ao projeto correspondente.
 *   **RF08 - Registro de Decisões do Cliente (Rastreabilidade):** O sistema deve possuir um log específico para registrar decisões estratégicas e aprovações formais realizadas junto ao cliente, garantindo um histórico imutável para futuras consultas.
-*   **RF09 - Mapeamento do Ciclo de Vida do Projeto (Fases da EJCM):** O sistema deve permitir categorizar e acompanhar o progresso do projeto de acordo com as etapas de entrega da EJCM: Pesquisa, Prototipação, Desenvolvimento, e Entrega e Suporte.
+*   **RF09 - Mapeamento do Ciclo de Vida do Projeto (Fases da &lt;Empresa Júnior&gt;):** O sistema deve permitir categorizar e acompanhar o progresso do projeto de acordo com as etapas de entrega da &lt;Empresa Júnior&gt;: Pesquisa, Prototipação, Desenvolvimento, e Entrega e Suporte.
 *   **RF10 - Busca Global Avançada:** O sistema deve fornecer uma barra de pesquisa global que permita localizar rapidamente tarefas, atas de reuniões, decisões homologadas e documentos anexos em qualquer projeto ativo ou arquivado.
 *   **RF11 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve permitir a definição de permissões de acesso diferenciadas (Ex: Gerente de Projetos, Membro do Squad, Cliente, Administrador), garantindo que clientes visualizem apenas informações autorizadas.
 *   **RF12 - Integração com Ferramentas Externas:** O sistema deve permitir a integração ou importação de dados de ferramentas legadas de mercado (como Notion, Trello, Google Drive e Clockify) para facilitar a migração de dados de projetos em andamento.
@@ -201,7 +201,7 @@
 *   **RNF02 - Compatibilidade Multiplataforma (Responsividade):** O sistema deve ser uma aplicação web responsiva, compatível com os principais navegadores do mercado (Chrome, Firefox, Safari, Edge) e otimizada para uso em computadores pessoais e corporativos de diferentes sistemas operacionais (Windows, macOS e Linux).
 *   **RNF03 - Desempenho de Busca:** A ferramenta de busca global deve retornar resultados relevantes em menos de 2 segundos, mesmo em bases de dados com grande volume de documentos e históricos acumulados.
 *   **RNF04 - Confiabilidade e Salvamento Automático:** O sistema deve possuir um mecanismo de salvamento automático para a edição de documentos, atas de reuniões e descrições de tarefas, evitando a perda de dados por falhas de conexão ou fechamento acidental da aba.
-*   **RNF05 - Segurança e Privacidade dos Dados:** O sistema deve garantir a criptografia dos dados em trânsito (HTTPS) e em repouso, protegendo as informações estratégicas da EJCM e os dados confidenciais dos clientes.
+*   **RNF05 - Segurança e Privacidade dos Dados:** O sistema deve garantir a criptografia dos dados em trânsito (HTTPS) e em repouso, protegendo as informações estratégicas da &lt;Empresa Júnior&gt; e os dados confidenciais dos clientes.
 *   **RNF06 - Disponibilidade:** O sistema deve estar disponível para uso diário contínuo com uma taxa de disponibilidade de, no mínimo, 99,5% (uptime).
 *   **RNF07 - Integridade do Histórico (Backup):** O sistema deve realizar backups diários automatizados e garantir que os históricos de decisões do cliente e encerramento de projetos não possam ser apagados ou alterados retroativamente sem autorização especial do administrador.
 </t>
@@ -222,13 +222,13 @@
 *   **RF06 - Versionamento de Documentos:** O sistema deve controlar o versionamento de propostas comerciais e contratos anexados, registrando o histórico de alterações, a data da modificação e o membro responsável.
 *   **RF07 - Automação de Fluxo de Trabalho Comercial:** O sistema deve automatizar tarefas repetitivas do processo de vendas, como a alteração automática do status do lead no funil ao anexar uma proposta comercial ou ao agendar uma reunião de diagnóstico.
 *   **RF08 - Integração Vendas-Projetos:** O sistema deve permitir a conversão automática de um lead ganho em um novo projeto, transferindo o histórico de negociação, escopo aprovado e documentos para o módulo de gerenciamento de projetos (etapas de Pesquisa, Prototipação e Desenvolvimento).
-*   **RF09 - Painel de Desempenho Comercial (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real com indicadores de desempenho (KPIs), incluindo taxa de conversão do funil, tempo médio de venda, quantidade de leads ativos e progresso em relação às metas anuais da EJCM.
+*   **RF09 - Painel de Desempenho Comercial (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real com indicadores de desempenho (KPIs), incluindo taxa de conversão do funil, tempo médio de venda, quantidade de leads ativos e progresso em relação às metas anuais da &lt;Empresa Júnior&gt;.
 *   **RF10 - Sistema de Alertas e Notificações:** O sistema deve enviar notificações internas (alertas no sistema e e-mails) para os assessores de vendas sobre tarefas pendentes, reuniões agendadas, leads sem interação recente ou propostas que necessitam de acompanhamento (follow-up).
 *   **RF11 - Registro de Auditoria (Logs):** O sistema deve registrar um log detalhado de todas as ações críticas realizadas sobre os dados de clientes, propostas e contratos, identificando o usuário que realizou a operação, a data e a hora.
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a informações confidenciais (dados de clientes, faturamento e contratos) por meio de perfis de permissão (ex.: Administrador, Assessor de Vendas, Desenvolvedor).
 *   **RNF02 - Segurança e Proteção de Dados:** O sistema deve garantir a proteção dos dados dos clientes em conformidade com as diretrizes da LGPD, utilizando criptografia de dados em repouso e em trânsito (HTTPS/TLS).
-*   **RNF03 - Compatibilidade e Acesso Web:** O sistema deve ser acessível via navegadores web modernos (Chrome, Firefox, Safari, Edge) a partir de computadores pessoais (desktops e notebooks) dos membros da EJCM, sem necessidade de instalação de softwares locais.
+*   **RNF03 - Compatibilidade e Acesso Web:** O sistema deve ser acessível via navegadores web modernos (Chrome, Firefox, Safari, Edge) a partir de computadores pessoais (desktops e notebooks) dos membros da &lt;Empresa Júnior&gt;, sem necessidade de instalação de softwares locais.
 *   **RNF04 - Desempenho de Busca:** A busca avançada por propostas e documentos históricos deve retornar resultados em um tempo máximo de 2 segundos, mesmo com o crescimento da base de dados.
 *   **RNF05 - Disponibilidade:** O sistema deve possuir uma disponibilidade de, no mínimo, 99,5% do tempo, garantindo que a equipe comercial possa acessar as informações continuamente ao longo do ano.
 *   **RNF06 - Usabilidade e Interface Responsiva:** A interface do usuário deve ser intuitiva, responsiva e otimizada para minimizar a quantidade de cliques necessários para registrar informações de vendas, visando o aumento da produtividade e a redução do retrabalho.</t>
@@ -252,16 +252,16 @@
 *   **RF09 - Integração de Artefatos de Design e UX:** O sistema deve permitir a associação de links externos (como protótipos do Figma) e documentos de pesquisa de UX diretamente à pasta do projeto ou do lead.
 *   **RF10 - Automação de Tarefas Repetitivas (Follow-up):** O sistema deve permitir a configuração de réguas de automação para disparar e-mails de acompanhamento (follow-up) ou criar tarefas automáticas para os assessores quando um lead permanecer inativo por um período pré-determinado em uma etapa do funil.
 *   **RF11 - Central de Notificações e Lembretes:** O sistema deve enviar notificações e lembretes aos assessores de vendas sobre reuniões agendadas, tarefas pendentes e prazos de envio de propostas.
-*   **RF12 - Dashboard de Desempenho Comercial:** O sistema deve gerar relatórios visuais e gráficos com indicadores de desempenho (KPIs), incluindo taxa de conversão do funil, tempo médio de fechamento, volume de novos leads e progresso em relação às metas anuais da EJCM.
+*   **RF12 - Dashboard de Desempenho Comercial:** O sistema deve gerar relatórios visuais e gráficos com indicadores de desempenho (KPIs), incluindo taxa de conversão do funil, tempo médio de fechamento, volume de novos leads e progresso em relação às metas anuais da &lt;Empresa Júnior&gt;.
 *   **RF13 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve permitir a definição de diferentes níveis de permissão de acesso (ex: Administrador, Assessor de Vendas, Desenvolvedor, Membro de Projeto), restringindo a visualização e edição de dados sensíveis de acordo com a função do usuário.
 *   **RF14 - Registro de Auditoria (Logs):** O sistema deve registrar um histórico de auditoria (logs) contendo as ações de criação, alteração e exclusão de dados de clientes, propostas e contratos, identificando o usuário e a data/hora da ação.
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 - Segurança e Proteção de Dados (LGPD):** O sistema deve criptografar os dados sensíveis dos clientes e contratos em repouso e em trânsito (utilizando HTTPS), garantindo a conformidade com a Lei Geral de Proteção de Dados (LGPD).
 *   **RNF02 - Compatibilidade e Responsividade:** O sistema deve ser responsivo e totalmente compatível com os principais navegadores web do mercado (Chrome, Firefox, Safari, Edge), garantindo o acesso adequado a partir de computadores pessoais (desktops e notebooks) dos membros.
-*   **RNF03 - Usabilidade e Curva de Aprendizado:** O sistema deve possuir uma interface intuitiva e de fácil usabilidade, permitindo que novos membros da EJCM consigam operá-lo com um treinamento básico de no máximo 2 horas.
+*   **RNF03 - Usabilidade e Curva de Aprendizado:** O sistema deve possuir uma interface intuitiva e de fácil usabilidade, permitindo que novos membros da &lt;Empresa Júnior&gt; consigam operá-lo com um treinamento básico de no máximo 2 horas.
 *   **RNF04 - Desempenho na Busca:** O mecanismo de busca global por propostas históricas e documentos deve retornar os resultados em um tempo máximo de 2 segundos, mesmo sob alto volume de dados acumulados.
 *   **RNF05 - Disponibilidade:** O sistema deve apresentar uma disponibilidade (uptime) mínima de 99,5%, garantindo que os assessores de vendas possam acessar as informações comerciais continuamente ao longo do ano.
-*   **RNF06 - Preservação do Conhecimento (Backup):** O sistema deve realizar backups automáticos e diários de todo o banco de dados e arquivos armazenados, garantindo a integridade e a preservação do histórico institucional ao longo das gestões da EJCM.
+*   **RNF06 - Preservação do Conhecimento (Backup):** O sistema deve realizar backups automáticos e diários de todo o banco de dados e arquivos armazenados, garantindo a integridade e a preservação do histórico institucional ao longo das gestões da &lt;Empresa Júnior&gt;.
 *   **RNF07 - Escalabilidade:** A arquitetura do sistema deve ser escalável, permitindo o aumento do volume de dados (leads, atas, propostas e projetos) e do número de usuários ativos simultâneos sem degradação do desempenho do software.</t>
   </si>
   <si>
@@ -278,16 +278,16 @@
 * **RF07 - Busca Global Avançada:** O sistema deve disponibilizar um mecanismo de busca que permita localizar rapidamente clientes, propostas antigas, atas de reuniões e documentos históricos por meio de palavras-chave, tags, datas ou filtros específicos.
 * **RF08 - Transição automática de Vendas para Projetos:** O sistema deve permitir que, ao marcar um lead como "Ganho" no funil de vendas, os dados do cliente e a proposta aprovada sejam convertidos automaticamente em um novo projeto na área de desenvolvimento, notificando a equipe técnica.
 * **RF09 - Automação de Tarefas e Lembretes:** O sistema deve criar tarefas automáticas e enviar alertas (notificações internas ou por e-mail) para os assessores de vendas sobre atividades pendentes, reuniões agendadas ou leads sem interação há determinado período.
-* **RF10 - Painel de Indicadores Comerciais (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real com indicadores de desempenho comercial, tais como taxa de conversão de leads, tempo médio de negociação, volume de vendas e progresso em relação às metas anuais da EJCM.
+* **RF10 - Painel de Indicadores Comerciais (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real com indicadores de desempenho comercial, tais como taxa de conversão de leads, tempo médio de negociação, volume de vendas e progresso em relação às metas anuais da &lt;Empresa Júnior&gt;.
 * **RF11 - Vinculação de Artefatos de Design e Desenvolvimento:** O sistema deve permitir a associação de links externos (como protótipos do Figma e repositórios de código) diretamente na página do projeto ou do lead correspondente.
 * **RF12 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve permitir a atribuição de diferentes níveis de permissão para os usuários (ex: Administrador, Assessor de Vendas, Desenvolvedor), restringindo o acesso a informações comerciais confidenciais e dados financeiros.
 * **RF13 - Log de Auditoria:** O sistema deve registrar um histórico detalhado e não editável de todas as ações críticas realizadas na plataforma, incluindo quem visualizou, editou ou excluiu dados de clientes, propostas ou contratos.
 ---
 ### Requisitos Não Funcionais (RNF)
-* **RNF01 - Segurança e Proteção de Dados (LGPD):** O sistema deve garantir a proteção dos dados pessoais dos clientes e membros da EJCM, utilizando criptografia para dados em trânsito (HTTPS) e em repouso, em conformidade com a Lei Geral de Proteção de Dados.
+* **RNF01 - Segurança e Proteção de Dados (LGPD):** O sistema deve garantir a proteção dos dados pessoais dos clientes e membros da &lt;Empresa Júnior&gt;, utilizando criptografia para dados em trânsito (HTTPS) e em repouso, em conformidade com a Lei Geral de Proteção de Dados.
 * **RNF02 - Compatibilidade e Responsividade:** O sistema deve ser totalmente responsivo e compatível com os principais navegadores web do mercado (Google Chrome, Mozilla Firefox, Safari e Microsoft Edge) para permitir o acesso seguro a partir de computadores pessoais dos membros.
 * **RNF03 - Desempenho na Busca:** O mecanismo de busca avançada deve retornar resultados em tempo inferior a 2 segundos, mesmo quando realizada em grandes volumes de dados históricos.
-* **RNF04 - Backup e Recuperação de Desastres:** O sistema deve realizar backups automatizados diários de todo o banco de dados e arquivos armazenados, garantindo a recuperação das informações em caso de falhas e evitando a perda do conhecimento organizacional da EJCM.
+* **RNF04 - Backup e Recuperação de Desastres:** O sistema deve realizar backups automatizados diários de todo o banco de dados e arquivos armazenados, garantindo a recuperação das informações em caso de falhas e evitando a perda do conhecimento organizacional da &lt;Empresa Júnior&gt;.
 * **RNF05 - Facilidade de Integração (API):** O sistema deve possuir uma arquitetura baseada em APIs para viabilizar futuras integrações diretas com ferramentas externas de prospecção ou comunicação (como Apollo e Pipefy).</t>
   </si>
   <si>
@@ -307,14 +307,14 @@
 *   **RF07 - Automação de Fluxo de Trabalho Comercial:** O sistema deve permitir a criação de regras de automação, como o envio automático de e-mails de acompanhamento (follow-up) e a criação de tarefas pendentes quando um lead mudar de etapa no pipeline.
 *   **RF08 - Transição de Vendas para Projetos:** O sistema deve permitir a conversão automática de um lead ganho em um novo projeto na base de dados, migrando o histórico comercial, a proposta aprovada e os dados do cliente para a equipe de desenvolvimento.
 *   **RF09 - Vinculação de Artefatos Técnicos:** O sistema deve permitir a associação de links externos de protótipos (ex: Figma), repositórios e documentos de pesquisa de UX diretamente à proposta comercial ou ao projeto integrado.
-*   **RF10 - Painel de Indicadores de Desempenho (Dashboards):** O sistema deve gerar relatórios e gráficos em tempo real com indicadores comerciais, incluindo taxa de conversão de leads, tempo médio em cada etapa do funil, faturamento projetado e progresso em relação às metas anuais da EJCM.
+*   **RF10 - Painel de Indicadores de Desempenho (Dashboards):** O sistema deve gerar relatórios e gráficos em tempo real com indicadores comerciais, incluindo taxa de conversão de leads, tempo médio em cada etapa do funil, faturamento projetado e progresso em relação às metas anuais da &lt;Empresa Júnior&gt;.
 *   **RF11 - Sistema de Notificações e Lembretes:** O sistema deve enviar notificações internas e alertas por e-mail sobre tarefas atrasadas, reuniões agendadas, necessidade de follow-up e atualizações em propostas sob responsabilidade do membro.
 *   **RF12 - Registro de Auditoria (Logs):** O sistema deve registrar de forma automática todas as alterações realizadas em dados críticos (como valores de propostas, exclusão de leads ou alteração de contratos), indicando o usuário responsável, a data e a modificação feita.
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 - Segurança e Proteção de Dados:** O sistema deve garantir a proteção dos dados dos clientes e leads armazenados, utilizando criptografia de dados em repouso e em trânsito (HTTPS), em conformidade com as diretrizes da LGPD.
-*   **RNF02 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a dados financeiros, contratos e propostas por meio de permissões de usuário específicas para diferentes cargos dentro da EJCM (ex: Assessoria, Diretoria, Desenvolvedor).
+*   **RNF02 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a dados financeiros, contratos e propostas por meio de permissões de usuário específicas para diferentes cargos dentro da &lt;Empresa Júnior&gt; (ex: Assessoria, Diretoria, Desenvolvedor).
 *   **RNF03 - Disponibilidade e Acesso Web:** O sistema deve ser hospedado em nuvem e acessível via navegadores web modernos (Chrome, Firefox, Safari, Edge) a partir de computadores pessoais dos membros, sem necessidade de instalação de software local.
-*   **RNF04 - Usabilidade e Responsividade:** A interface do sistema deve ser responsiva (adaptável a diferentes tamanhos de tela) e seguir padrões de usabilidade que minimizem o tempo de aprendizado e facilitem a transição de novos membros da EJCM.
+*   **RNF04 - Usabilidade e Responsividade:** A interface do sistema deve ser responsiva (adaptável a diferentes tamanhos de tela) e seguir padrões de usabilidade que minimizem o tempo de aprendizado e facilitem a transição de novos membros da &lt;Empresa Júnior&gt;.
 *   **RNF05 - Centralização de Ferramentas:** O sistema deve ser projetado para consolidar as funcionalidades de CRM, gestão de documentos e acompanhamento de tarefas, visando eliminar a dependência operacional direta de ferramentas externas fragmentadas (como Pipefy, Notion e Apollo).</t>
   </si>
   <si>
@@ -329,7 +329,7 @@
 *   **RF05 – Automação de Fluxos de Trabalho:** O sistema deve automatizar tarefas repetitivas do processo comercial, como a criação automática de uma tarefa de "Elaborar Proposta" quando o lead for movido para a etapa de "Proposta" no pipeline.
 *   **RF06 – Integração Comercial-Projetos:** O sistema deve permitir que, ao marcar um lead como "Contrato Fechado", as informações comerciais, proposta aprovada e escopo do projeto sejam automaticamente importadas para a área de gestão de projetos do sistema.
 *   **RF07 – Registro de Atas de Reunião:** O sistema deve possuir um editor de texto integrado para criação, salvamento e vinculação de atas de reuniões de diagnóstico e negociação diretamente ao cadastro do lead.
-*   **RF08 – Painel de Indicadores Comerciais (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real contendo métricas de desempenho, tais como: taxa de conversão do funil, tempo médio de fechamento, número de novos leads e progresso em relação às metas anuais da EJCM.
+*   **RF08 – Painel de Indicadores Comerciais (Dashboard):** O sistema deve gerar gráficos e relatórios em tempo real contendo métricas de desempenho, tais como: taxa de conversão do funil, tempo médio de fechamento, número de novos leads e progresso em relação às metas anuais da &lt;Empresa Júnior&gt;.
 *   **RF09 – Sistema de Notificações e Lembretes:** O sistema deve enviar notificações na plataforma e alertas por e-mail para os assessores de vendas sobre reuniões agendadas, propostas pendentes de retorno e tarefas atrasadas.
 *   **RF10 – Controle de Acesso Baseado em Perfis:** O sistema deve permitir a atribuição de permissões de acesso diferenciadas (ex.: Administrador, Assessor de Vendas, Desenvolvedor), restringindo a edição de propostas e a visualização de dados financeiros de clientes a usuários autorizados.
 *   **RF11 – Registro de Auditoria (Logs):** O sistema deve registrar um histórico de alterações (logs) contendo usuário, data, hora e a modificação realizada em dados sensíveis de leads, propostas e contratos.
@@ -340,7 +340,7 @@
 *   **RNF03 – Desempenho e Tempo de Resposta:** O sistema deve apresentar um tempo de resposta inferior a 2 segundos para o carregamento do pipeline de vendas e para a execução de buscas na base de dados.
 *   **RNF04 – Facilidade de Integração (Interoperabilidade):** O sistema deve disponibilizar APIs ou ferramentas de importação de dados para viabilizar a migração das informações atualmente dispersas em plataformas externas (como Pipefy, Notion, Apollo e Figma).
 *   **RNF05 – Disponibilidade:** O sistema deve possuir uma taxa de disponibilidade mínima de 99,5% (uptime), garantindo que a equipe de vendas possa acessar as informações continuamente ao longo do ano.
-*   **RNF06 – Usabilidade:** A interface do usuário deve ser intuitiva, padronizada e de fácil adoção, reduzindo o tempo de treinamento necessário para novos integrantes da EJCM.
+*   **RNF06 – Usabilidade:** A interface do usuário deve ser intuitiva, padronizada e de fácil adoção, reduzindo o tempo de treinamento necessário para novos integrantes da &lt;Empresa Júnior&gt;.
 </t>
   </si>
   <si>
@@ -366,7 +366,7 @@
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 – Segurança e Criptografia de Dados:** O sistema deve criptografar todos os dados pessoais sensíveis armazenados no banco de dados (criptografia em repouso) e utilizar protocolo seguro HTTPS para a transmissão de dados (criptografia em trânsito).
 *   **RNF02 – Conformidade Legal (LGPD):** O sistema deve ser projetado em conformidade com as diretrizes da Lei Geral de Proteção de Dados (LGPD), garantindo o consentimento explícito para o tratamento de dados e ferramentas para a portabilidade e exclusão de informações pessoais.
-*   **RNF03 – Disponibilidade e Acesso Multiplataforma:** O sistema deve ser baseado em web (SaaS), garantindo disponibilidade mínima de 99,5% e permitindo acesso seguro tanto de computadores locais na sede da EJCM quanto de dispositivos pessoais remotamente.
+*   **RNF03 – Disponibilidade e Acesso Multiplataforma:** O sistema deve ser baseado em web (SaaS), garantindo disponibilidade mínima de 99,5% e permitindo acesso seguro tanto de computadores locais na sede da &lt;Empresa Júnior&gt; quanto de dispositivos pessoais remotamente.
 *   **RNF04 – Autenticação Segura:** O acesso remoto ao sistema por usuários com privilégios administrativos (como a Assessora de GP) deve exigir autenticação multifator (MFA).
 *   **RNF05 – Facilidade de Uso e Configuração (Usabilidade):** A interface de criação de pesquisas e automação de fluxos de dados deve ser intuitiva e amigável (no-code/low-code), permitindo que a assessora gerencie os processos sem a necessidade de suporte ou conhecimento técnico em programação.
 *   **RNF06 – Backup e Recuperação de Desastres:** O sistema deve realizar rotinas diárias de backup automatizado incremental de todos os dados e documentos cadastrados, com um plano de recuperação que garanta a restauração dos dados em caso de falhas.
@@ -376,7 +376,7 @@
   <si>
     <t>### Requisitos Funcionais (RF)
 *   **RF01 - Cadastro Centralizado de Membros:** O sistema deve permitir o cadastro, edição, consulta e visualização de dados pessoais e administrativos de membros e ex-membros (incluindo nome, RG, CPF, endereço, idade, e-mail, telefone, cargo e área).
-*   **RF02 - Histórico de Membros:** O sistema deve manter um histórico consolidado e cronológico da trajetória de cada membro na EJCM, registrando datas de admissão, desligamento, promoções, projetos realizados e feedbacks.
+*   **RF02 - Histórico de Membros:** O sistema deve manter um histórico consolidado e cronológico da trajetória de cada membro na &lt;Empresa Júnior&gt;, registrando datas de admissão, desligamento, promoções, projetos realizados e feedbacks.
 *   **RF03 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a dados pessoais sensíveis dos membros, permitindo que apenas usuários autorizados (como a Assessoria de Gestão de Pessoas) visualizem, editem ou excluam essas informações.
 *   **RF04 - Gestão de Contratos e Termos:** O sistema deve permitir o upload, armazenamento e associação de contratos, termos de voluntariado, termos de confidencialidade e outros documentos administrativos ao perfil de cada membro.
 *   **RF05 - Geração Automatizada de Documentos:** O sistema deve gerar automaticamente documentos e termos administrativos preenchidos a partir de modelos pré-configurados e dos dados cadastrais dos membros.
@@ -390,7 +390,7 @@
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 - Conformidade com a LGPD:** O sistema deve criptografar dados pessoais sensíveis (como CPF, RG e endereços) tanto em repouso (banco de dados) quanto em trânsito (protocolo HTTPS) para garantir a conformidade com a Lei Geral de Proteção de Dados.
 *   **RNF02 - Autenticação Segura (MFA):** O sistema deve exigir autenticação de múltiplos fatores (MFA) para o acesso de administradores e assessores com privilégios de manipulação de dados sensíveis.
-*   **RNF03 - Disponibilidade e Acesso Remoto:** O sistema deve ser baseado em plataforma web, sendo acessível de forma segura tanto computadores da sede da EJCM quanto de dispositivos pessoais externos, com uma disponibilidade mínima de 99,5%.
+*   **RNF03 - Disponibilidade e Acesso Remoto:** O sistema deve ser baseado em plataforma web, sendo acessível de forma segura tanto computadores da sede da &lt;Empresa Júnior&gt; quanto de dispositivos pessoais externos, com uma disponibilidade mínima de 99,5%.
 *   **RNF04 - Tolerância a Falhas nas Integrações:** O sistema deve possuir um mecanismo de reprocessamento e tratamento de erros para garantir que falhas temporárias de rede não causem perda de dados vindos de formulários integrados.
 *   **RNF05 - Facilidade de Uso (Usabilidade):** A interface de configuração de pesquisas e automações deve ser intuitiva, permitindo que a Assessora de GP realize tarefas operacionais sem a necessidade de suporte técnico ou conhecimento em programação.
 *   **RNF06 - Backup e Recuperação:** O sistema deve realizar rotinas diárias e automáticas de backup incremental de todos os dados cadastrais e documentos, garantindo um tempo de recuperação (RTO) de no máximo 4 horas em caso de falhas críticas.</t>
@@ -401,11 +401,11 @@
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
 *   **RF01 – Cadastro Centralizado de Membros:** O sistema deve permitir o cadastro, consulta, atualização e exclusão de dados pessoais e administrativos de membros e ex-membros (incluindo nome completo, RG, CPF, endereço, data de nascimento, e-mail e telefone).
-*   **RF02 – Histórico do Membro:** O sistema deve manter um registro histórico consolidado da trajetória de cada membro na EJCM, incluindo cargos ocupados, projetos realizados, avaliações de desempenho e feedbacks recebidos.
+*   **RF02 – Histórico do Membro:** O sistema deve manter um registro histórico consolidado da trajetória de cada membro na &lt;Empresa Júnior&gt;, incluindo cargos ocupados, projetos realizados, avaliações de desempenho e feedbacks recebidos.
 *   **RF03 – Gestão de Documentos e Termos:** O sistema deve permitir o upload, armazenamento, organização e download de documentos formais, termos de voluntariado, contratos e acordos de confidencialidade vinculados ao perfil de cada membro.
 *   **RF04 – Geração Automatizada de Documentos:** O sistema deve gerar automaticamente contratos e termos administrativos em formato PDF a partir de modelos pré-definidos, preenchendo automaticamente os campos com os dados cadastrais do membro selecionado.
 *   **RF05 – Integração com Formulários Externos:** O sistema deve possuir integração automatizada com ferramentas de formulários (como Google Forms ou Typeform) para coletar dados de processos seletivos e pesquisas, atualizando a base de dados interna sem necessidade de digitação manual.
-*   **RF06 – Gestão de Pesquisas de Clima:** O sistema deve permitir a criação, agendamento e envio periódico (semanal/mensal) de pesquisas de clima organizacional e de satisfação para os membros da EJCM.
+*   **RF06 – Gestão de Pesquisas de Clima:** O sistema deve permitir a criação, agendamento e envio periódico (semanal/mensal) de pesquisas de clima organizacional e de satisfação para os membros da &lt;Empresa Júnior&gt;.
 *   **RF07 – Painel de Indicadores de Gestão de Pessoas (Dashboard):** O sistema deve gerar gráficos e relatórios consolidados em tempo real sobre os resultados das pesquisas de clima, engajamento dos membros e relacionamento entre as equipes.
 *   **RF08 – Notificações e Alertas Automáticos:** O sistema deve enviar notificações automáticas para os membros sobre pendências de preenchimento de pesquisas, assinatura de termos ou entrega de documentos obrigatórios.
 *   **RF09 – Importação e Exportação de Dados:** O sistema deve permitir a importação e exportação de dados cadastrais e relatórios de pesquisas em formatos padronizados (como CSV ou XLSX) de forma simplificada.
@@ -415,7 +415,7 @@
 *   **RNF01 – Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve restringir o acesso a dados pessoais sensíveis (como CPF, RG e avaliações individuais), permitindo a visualização e edição desses dados apenas a usuários com o perfil de "Assessoria de Gestão de Pessoas" ou administradores autorizados.
 *   **RNF02 – Segurança e Criptografia de Dados:** Todos os dados pessoais sensíveis armazenados no banco de dados e as informações trafegadas entre o cliente e o servidor devem ser criptografados (utilizando HTTPS e algoritmos de criptografia em repouso).
 *   **RNF03 – Conformidade Legal (LGPD):** O sistema deve ser desenvolvido em estrita conformidade com a Lei Geral de Proteção de Dados (LGPD), garantindo o consentimento explícito para coleta de dados e mecanismos fáceis para auditoria e exclusão de informações.
-*   **RNF04 – Disponibilidade e Acesso Remoto Seguro:** O sistema deve ser baseado em nuvem (SaaS), garantindo disponibilidade de 99,5% e permitindo o acesso seguro tanto dos computadores da sede da EJCM quanto de dispositivos pessoais externos, mediante autenticação segura de dois fatores (MFA).
+*   **RNF04 – Disponibilidade e Acesso Remoto Seguro:** O sistema deve ser baseado em nuvem (SaaS), garantindo disponibilidade de 99,5% e permitindo o acesso seguro tanto dos computadores da sede da &lt;Empresa Júnior&gt; quanto de dispositivos pessoais externos, mediante autenticação segura de dois fatores (MFA).
 *   **RNF05 – Backup e Recuperação de Desastres:** O sistema deve realizar rotinas diárias de backup automatizado de todos os dados de membros e documentos, com tempo de recuperação (RTO) máximo de 4 horas em caso de falha crítica.
 *   **RNF06 – Usabilidade e Facilidade de Configuração:** A interface para configuração de integrações e geração de relatórios deve ser intuitiva e não exigir conhecimentos de programação ou codificação por parte da Assessora de Gestão de Pessoas.
 </t>
@@ -427,7 +427,7 @@
     <t>### Requisitos Funcionais (RF)
 *   **RF01 - Cadastro e Gestão Unificada de Membros:** O sistema deve permitir o cadastro, edição, consulta e exclusão de dados pessoais e administrativos de membros e ex-membros (incluindo RG, CPF, endereço, idade, cargo, área e histórico na organização).
 *   **RF02 - Controle de Acesso Baseado em Perfis (RBAC):** O sistema deve permitir a criação de perfis de acesso distintos (ex: Assessora de GP, Diretoria, Membro), garantindo que dados sensíveis de membros sejam visualizados e editados apenas por usuários autorizados.
-*   **RF03 - Histórico Consolidado de Membros:** O sistema deve manter um registro histórico de toda a trajetória do membro na EJCM, incluindo promoções, desligamentos, feedbacks, avaliações de desempenho e projetos em que participou.
+*   **RF03 - Histórico Consolidado de Membros:** O sistema deve manter um registro histórico de toda a trajetória do membro na &lt;Empresa Júnior&gt;, incluindo promoções, desligamentos, feedbacks, avaliações de desempenho e projetos em que participou.
 *   **RF04 - Gestão de Documentos e Termos:** O sistema deve permitir o upload, armazenamento, organização e download de contratos de voluntariado, termos de confidencialidade (NDA) e outros documentos administrativos associados ao cadastro de cada membro.
 *   **RF05 - Geração Automatizada de Documentos:** O sistema deve gerar automaticamente documentos, contratos e termos administrativos em formato PDF a partir de modelos pré-definidos, preenchendo-os com os dados cadastrais do membro armazenados no sistema.
 *   **RF06 - Integração Automatizada de Formulários:** O sistema deve possuir integração com ferramentas de formulários digitais externos para coletar, consolidar e atualizar dados cadastrais de novos membros de forma automática, eliminando a necessidade de inserção manual.
@@ -452,7 +452,7 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 – Cadastro Unificado de Membros e Ex-membros:** O sistema deve permitir o cadastro, consulta, edição e inativação de registros de membros e ex-membros, centralizando dados pessoais (nome, RG, CPF, endereço, telefone, e-mail) e histórico de atuação na EJCM.
+*   **RF01 – Cadastro Unificado de Membros e Ex-membros:** O sistema deve permitir o cadastro, consulta, edição e inativação de registros de membros e ex-membros, centralizando dados pessoais (nome, RG, CPF, endereço, telefone, e-mail) e histórico de atuação na &lt;Empresa Júnior&gt;.
 *   **RF02 – Gestão de Documentos e Termos:** O sistema deve permitir o upload, armazenamento, organização e download de documentos digitais, termos de voluntariado, contratos e acordos de confidencialidade vinculados diretamente ao perfil de cada membro.
 *   **RF03 – Geração Automatizada de Documentos:** O sistema deve gerar automaticamente contratos e termos administrativos em formato PDF a partir de modelos personalizáveis, preenchendo os campos com os dados cadastrais do membro selecionado.
 *   **RF04 – Integração com Formulários Externos:** O sistema deve integrar-se a ferramentas de formulários digitais para capturar e atualizar automaticamente os dados de novos membros e pesquisas de opinião no banco de dados central, eliminando a inserção manual.
@@ -466,7 +466,7 @@
 ---
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 – Segurança e Criptografia (Conformidade com a LGPD):** O sistema deve criptografar dados pessoais sensíveis armazenados no banco de dados (criptografia em repouso) e utilizar protocolo seguro HTTPS para toda a comunicação de dados (criptografia em trânsito).
-*   **RNF02 – Autenticação Segura Multi-fator (MFA):** O sistema deve exigir autenticação de dois fatores (MFA) para acessos administrativos realizados fora da rede local (sede física da EJCM).
+*   **RNF02 – Autenticação Segura Multi-fator (MFA):** O sistema deve exigir autenticação de dois fatores (MFA) para acessos administrativos realizados fora da rede local (sede física da &lt;Empresa Júnior&gt;).
 *   **RNF03 – Disponibilidade e Acesso Remoto:** O sistema deve ser implantado em ambiente web (nuvem), garantindo disponibilidade de no mínimo 99,5% do tempo, permitindo o acesso seguro tanto de computadores locais quanto de dispositivos pessoais externos.
 *   **RNF04 – Usabilidade e Configuração Sem Código (No-Code/Low-Code):** A interface de configuração de automações de dados e criação de pesquisas deve ser intuitiva e amigável, permitindo que a Assessora de GP realize manutenções operacionais sem a necessidade de conhecimento técnico em programação.
 *   **RNF05 – Robustez e Tolerância a Falhas:** O sistema deve validar e tratar erros de integração de dados de fontes externas, gerando relatórios de falha automáticos em caso de inconsistência, sem interromper o funcionamento das demais rotinas.
@@ -506,7 +506,7 @@
 *   **RF03 - Modelos de Documentação (Templates):** O sistema deve permitir a criação e o uso de templates padronizados para documentos técnicos (como especificação de arquitetura, manuais de implantação e relatórios de entrega).
 *   **RF04 - Controle de Versão de Documentos:** O sistema deve manter um histórico de alterações de todos os documentos e artigos da base de conhecimento, permitindo visualizar versões anteriores e identificar o autor de cada modificação.
 *   **RF05 - Busca Global Avançada:** O sistema deve fornecer uma ferramenta de busca textual que indexe todo o conteúdo de documentos, tarefas e projetos, com suporte a filtros por projeto, tecnologia, autor e data.
-*   **RF06 - Gestão de Permissões de Acesso:** O sistema deve permitir a configuração de níveis de acesso (leitura, escrita e administração) para documentos, projetos e pastas de acordo com o papel do membro na EJCM (ex: Líder Técnico, Desenvolvedor, Assessor).
+*   **RF06 - Gestão de Permissões de Acesso:** O sistema deve permitir a configuração de níveis de acesso (leitura, escrita e administração) para documentos, projetos e pastas de acordo com o papel do membro na &lt;Empresa Júnior&gt; (ex: Líder Técnico, Desenvolvedor, Assessor).
 *   **RF07 - Rastreabilidade de Contribuições:** O sistema deve registrar e exibir um histórico consolidado das atividades técnicas realizadas por cada membro nos projetos, integrado às fases de desenvolvimento (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
 *   **RF08 - Importação de Arquivos:** O sistema deve permitir a importação direta de arquivos em formatos comuns (como Markdown, PDF e DOCX) para facilitar a migração de conteúdos vindos do Notion ou Google Drive.
 *   **RF09 - Notificações de Atualizações Técnicas:** O sistema deve enviar notificações semanais consolidadas ao Líder Técnico contendo o resumo das alterações realizadas em documentos de projetos sob sua responsabilidade.
@@ -551,7 +551,7 @@
 *   **RF02 - Sistema de Gestão de Conhecimento (Wiki):** O sistema deve disponibilizar um módulo de base de conhecimento (estilo Wiki) para criação, edição e compartilhamento de artigos técnicos, guias de desenvolvimento e boas práticas.
 *   **RF03 - Controle de Versão de Documentos:** O sistema deve manter o histórico de alterações de cada documento técnico, permitindo visualizar versões anteriores, identificar o autor das modificações e restaurar versões passadas.
 *   **RF04 - Mecanismo de Busca Avançada:** O sistema deve possuir uma barra de busca global que permita encontrar rapidamente documentos, códigos, projetos e artigos de conhecimento por meio de palavras-chave, tags, autor ou data de modificação.
-*   **RF05 - Padronização por Templates:** O sistema deve fornecer templates editáveis para a criação de documentações técnicas específicas de cada etapa do ciclo de vida da EJCM (Pesquisa, Prototipação, Desenvolvimento e Entrega/Suporte).
+*   **RF05 - Padronização por Templates:** O sistema deve fornecer templates editáveis para a criação de documentações técnicas específicas de cada etapa do ciclo de vida da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento e Entrega/Suporte).
 *   **RF06 - Controle de Acesso e Permissões:** O sistema deve permitir definir diferentes níveis de permissão (leitura, edição, administração) para os membros da equipe em relação aos projetos e documentos técnicos.
 *   **RF07 - Rastreabilidade de Contribuições:** O sistema deve registrar de forma automática as atividades realizadas pelos membros nos artefatos dos projetos, indicando quem criou, alterou ou excluiu determinada informação.
 *   **RF08 - Automatização de Relatórios Semanais:** O sistema deve gerar automaticamente relatórios de status semanal dos projetos, consolidando as tarefas concluídas, pendentes e os artefatos técnicos gerados no período.
@@ -595,7 +595,7 @@
   <si>
     <t>### Requisitos Funcionais (RF)
 *   **RF01 - Cadastro e Centralização de Projetos:** O sistema deve permitir o cadastro de projetos, centralizando em uma única tela as informações de escopo, cronograma, equipe alocada, repositórios de código (links externos) e documentação técnica.
-*   **RF02 - Módulo de Definição e Elicitação de Requisitos:** O sistema deve disponibilizar um módulo para cadastro, detalhamento e categorização dos requisitos do projeto, associando-os às etapas do fluxo de desenvolvimento da EJCM (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
+*   **RF02 - Módulo de Definição e Elicitação de Requisitos:** O sistema deve disponibilizar um módulo para cadastro, detalhamento e categorização dos requisitos do projeto, associando-os às etapas do fluxo de desenvolvimento da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte).
 *   **RF03 - Histórico de Alterações de Requisitos (Versionamento):** O sistema deve registrar automaticamente qualquer alteração realizada nos requisitos de um projeto, armazenando o autor da modificação, a data, a versão anterior e a justificativa do ajuste.
 *   **RF04 - Rastreabilidade de Itens de Trabalho:** O sistema deve permitir vincular diretamente cada requisito cadastrado às suas respectivas tarefas no backlog e aos entregáveis correspondentes, garantindo a rastreabilidade de ponta a ponta.
 *   **RF05 - Base Histórica de Estimativas e Tarefas:** O sistema deve manter um registro consolidado de todas as tarefas executadas em projetos anteriores, contendo a descrição da atividade, a categoria (ex: desenvolvimento frontend, prototipação, pesquisa de UX), o tempo estimado e o tempo real de execução.
@@ -606,7 +606,7 @@
 *   **RF10 - Dashboard de Métricas de Produtividade:** O sistema deve disponibilizar um painel de indicadores para o Tech Lead, apresentando métricas como o tempo médio de execução por tipo de tarefa, taxa de retrabalho por alteração de escopo e índice de desvio de prazo dos projetos.
 ### Requisitos Não Funcionais (RNF)
 *   **RNF01 - Centralização de Dados (Consistência):** O sistema deve unificar os dados de projetos e tarefas em um banco de dados centralizado, eliminando a redundância de informações atualmente dispersas em planilhas e documentos isolados.
-*   **RNF02 - Facilidade de Uso e Interface Intuitiva (Usabilidade):** A interface de gestão de backlog e documentação deve ser fluida e amigável, inspirada em ferramentas de produtividade modernas (como Notion), para garantir a rápida adoção pelos membros da EJCM.
+*   **RNF02 - Facilidade de Uso e Interface Intuitiva (Usabilidade):** A interface de gestão de backlog e documentação deve ser fluida e amigável, inspirada em ferramentas de produtividade modernas (como Notion), para garantir a rápida adoção pelos membros da &lt;Empresa Júnior&gt;.
 *   **RNF03 - Desempenho na Consulta de Histórico:** A busca por tarefas históricas e lições aprendidas na base de conhecimento deve retornar resultados em menos de 2 segundos, mesmo com o crescimento do volume de dados ao longo dos anos.
 *   **RNF04 - Rastreabilidade e Auditabilidade:** Toda alteração de escopo, cronograma ou status de requisitos deve gerar um log de auditoria imutável para garantir a transparência do processo de gestão técnica.</t>
   </si>
@@ -629,7 +629,7 @@
 *   **RNF01 - Integração com Ferramentas de Produtividade:** O sistema deve permitir a importação e exportação de dados em formatos compatíveis com Google Sheets, Google Docs e Notion (ex: CSV, PDF, Markdown).
 *   **RNF02 - Desempenho em Consultas Históricas:** As consultas ao banco de dados histórico de tarefas e projetos anteriores devem retornar resultados em menos de 2 segundos, mesmo com o crescimento da base de dados.
 *   **RNF03 - Consistência e Imutabilidade de Dados Históricos:** Os registros de tarefas e tempos de execução de projetos já finalizados e arquivados devem ser de apenas leitura (imutáveis), garantindo a integridade dos dados para estimativas futuras.
-*   **RNF04 - Usabilidade e Curva de Aprendizado:** A interface de gestão de backlog e cronogramas deve ser intuitiva, seguindo padrões de usabilidade modernos (UX), de modo a reduzir a dependência de treinamentos individuais para novos membros da EJCM.</t>
+*   **RNF04 - Usabilidade e Curva de Aprendizado:** A interface de gestão de backlog e cronogramas deve ser intuitiva, seguindo padrões de usabilidade modernos (UX), de modo a reduzir a dependência de treinamentos individuais para novos membros da &lt;Empresa Júnior&gt;.</t>
   </si>
   <si>
     <t>Semelhante à iteração 1. Traz a geração de Gantt e Kanban, mas a quantidade de RNFs ficou na média.</t>
@@ -638,7 +638,7 @@
     <t>### Requisitos Funcionais (RF)
 *   **RF01 - Cadastro e Rastreabilidade de Requisitos:** O sistema deve permitir o cadastro detalhado de requisitos de projeto (funcionais e não funcionais) e possibilitar a vinculação direta de cada requisito às respectivas tarefas no backlog de desenvolvimento.
 *   **RF02 - Histórico de Alterações de Escopo (Change Log):** O sistema deve registrar e versionar automaticamente qualquer alteração realizada nos requisitos do projeto, armazenando a data da modificação, o autor da alteração e a justificativa técnica.
-*   **RF03 - Modelos de Projetos Padronizados (Templates):** O sistema deve permitir a criação e a aplicação de templates de projetos baseados nas etapas metodológicas da EJCM (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte), contendo estruturas de backlog e estimativas de esforço padrão.
+*   **RF03 - Modelos de Projetos Padronizados (Templates):** O sistema deve permitir a criação e a aplicação de templates de projetos baseados nas etapas metodológicas da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento, Entrega e Suporte), contendo estruturas de backlog e estimativas de esforço padrão.
 *   **RF04 - Registro e Acompanhamento de Tempo (Time Tracking):** O sistema deve permitir que os membros da equipe de desenvolvimento registrem o tempo real gasto na execução de cada tarefa associada ao projeto.
 *   **RF05 - Mecanismo de Busca de Histórico de Estimativas:** O sistema deve oferecer um filtro de busca avançada para que o Tech Lead pesquise tarefas e projetos passados por tecnologia, complexidade ou tipo de funcionalidade, exibindo o tempo médio real de execução dessas atividades para apoiar novas estimativas.
 *   **RF06 - Repositório Central de Documentação Técnica:** O sistema deve possuir um módulo integrado para criação, edição e armazenamento de documentações técnicas do projeto (como diagramas de arquitetura, especificações de APIs e guias de deploy).
@@ -683,13 +683,13 @@
     <t xml:space="preserve">### Requisitos Funcionais (RF)
 *   **RF01 - Vinculação de Repositórios:** O sistema deve permitir associar repositórios de código externos (ex: GitHub, GitLab) a cada projeto cadastrado na plataforma.
 *   **RF02 - Centralização de Documentação Técnica:** O sistema deve disponibilizar um módulo para criação, edição, categorização e armazenamento de documentos técnicos (especificações de arquitetura, diagramas e guias de API) vinculados a cada projeto.
-*   **RF03 - Templates de Levantamento de Requisitos:** O sistema deve fornecer templates padronizados para o preenchimento de requisitos de software, estruturados de acordo com as etapas de desenvolvimento da EJCM (Pesquisa, Prototipação, Desenvolvimento e Entrega).
+*   **RF03 - Templates de Levantamento de Requisitos:** O sistema deve fornecer templates padronizados para o preenchimento de requisitos de software, estruturados de acordo com as etapas de desenvolvimento da &lt;Empresa Júnior&gt; (Pesquisa, Prototipação, Desenvolvimento e Entrega).
 *   **RF04 - Rastreabilidade de Itens de Escopo:** O sistema deve permitir associar tarefas do backlog diretamente aos requisitos de software que as originaram, mantendo o vínculo visível durante todo o ciclo de vida do projeto.
 *   **RF05 - Histórico de Alterações de Requisitos (Versionamento):** O sistema deve registrar automaticamente qualquer alteração realizada nos requisitos do projeto, identificando o autor, a data, a hora, o campo alterado e exigindo a inserção de uma justificativa para a mudança.
 *   **RF06 - Registro de Tempo de Execução por Categoria:** O sistema deve registrar o tempo planejado versus o tempo real de execução de cada tarefa concluída, categorizando-as por tipo de atividade (ex: pesquisa de UX, prototipação, desenvolvimento frontend, desenvolvimento backend, testes).
 *   **RF07 - Base de Conhecimento e Busca Avançada:** O sistema deve disponibilizar um mecanismo de busca global que permita consultar tarefas, escopos, tecnologias utilizadas e lições aprendidas de projetos anteriores já concluídos.
 *   **RF08 - Gerador de Estimativas Baseado em Histórico:** O sistema deve fornecer uma funcionalidade de apoio à decisão que sugira prazos e esforços para novas tarefas com base na média de tempo de execução de tarefas similares registradas no histórico da organização.
-*   **RF09 - Cronograma Interativo com Linha do Tempo:** O sistema deve gerar e exibir um cronograma interativo (ex: Gráfico de Gantt) para cada projeto, permitindo a visualização de dependências entre tarefas, marcos de entrega (milestones) e o progresso em tempo real das etapas da EJCM.
+*   **RF09 - Cronograma Interativo com Linha do Tempo:** O sistema deve gerar e exibir um cronograma interativo (ex: Gráfico de Gantt) para cada projeto, permitindo a visualização de dependências entre tarefas, marcos de entrega (milestones) e o progresso em tempo real das etapas da &lt;Empresa Júnior&gt;.
 *   **RF10 - Registro de Lições Aprendidas (Post-Mortem):** O sistema deve disponibilizar um formulário de fechamento de projeto para que o Tech Lead registre as lições aprendidas, riscos mitigados e dificuldades técnicas enfrentadas pela equipe.
 ---
 ### Requisitos Não Funcionais (RNF)
@@ -707,9 +707,9 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 - Cadastro Unificado de Membros:** O sistema deve permitir o cadastro, edição, consulta e exclusão de perfis de membros da EJCM, contendo dados pessoais, contatos, cargo atual, assessoria correspondente e histórico de projetos em que participou.
+*   **RF01 - Cadastro Unificado de Membros:** O sistema deve permitir o cadastro, edição, consulta e exclusão de perfis de membros da &lt;Empresa Júnior&gt;, contendo dados pessoais, contatos, cargo atual, assessoria correspondente e histórico de projetos em que participou.
 *   **RF02 - Gerenciamento do Ciclo de Vida de Trainees:** O sistema deve permitir o registro e o acompanhamento completo de trainees, incluindo dados pessoais, cargo pretendido, controle de presença e tarefas realizadas no processo de treinamento, feedbacks recebidos e status de evolução técnica.
-*   **RF03 - Histórico de Movimentação de Membros:** O sistema deve registrar e exibir de forma cronológica o histórico de evolução de cada membro dentro da EJCM, detalhando promoções, mudanças de assessoria, desligamentos e projetos realizados.
+*   **RF03 - Histórico de Movimentação de Membros:** O sistema deve registrar e exibir de forma cronológica o histórico de evolução de cada membro dentro da &lt;Empresa Júnior&gt;, detalhando promoções, mudanças de assessoria, desligamentos e projetos realizados.
 *   **RF04 - Autenticação Unificada (Single Sign-On):** O sistema deve fornecer um mecanismo de login único para que o usuário acesse todas as funcionalidades internas de gestão de pessoas sem a necessidade de múltiplos logins ou alternância de contas.
 *   **RF05 - Integração com Ferramentas Externas:** O sistema deve integrar-se via APIs com Notion, Google Planilhas, Google Docs e Google Drive para permitir a importação, exportação e centralização de documentos e dados históricos de membros.
 *   **RF06 - Controle de Permissões de Acesso:** O sistema deve permitir a atribuição de perfis de acesso (ex: Administrador, Assessora de GP, Membro, Trainee), restringindo a edição e visualização de dados sensíveis e feedbacks apenas a usuários autorizados.
@@ -734,7 +734,7 @@
 *   **RF02 - Autenticação Unificada (Single Sign-On):** O sistema deve permitir o acesso de todos os usuários por meio de uma única credencial de login (ex: integração com a conta institucional do Google Workspace).
 *   **RF03 - Controle de Permissões de Acesso:** O sistema deve permitir a atribuição de perfis de acesso distintos (ex: Administrador, Assessora de GP, Membro, Trainee), restringindo a visualização e edição de dados sensíveis (como feedbacks e avaliações) de acordo com a função do usuário.
 *   **RF04 - Acompanhamento do Programa de Trainees:** O sistema deve disponibilizar um módulo específico para o acompanhamento de trainees, permitindo registrar e monitorar o progresso do treinamento técnico, as tarefas realizadas, as notas obtidas e os feedbacks recebidos.
-*   **RF05 - Histórico de Evolução e Movimentação:** O sistema deve registrar e manter de forma automatizada o histórico cronológico de cada integrante na EJCM, incluindo promoções, mudanças de cargo, troca de assessorias, projetos realizados e desligamentos.
+*   **RF05 - Histórico de Evolução e Movimentação:** O sistema deve registrar e manter de forma automatizada o histórico cronológico de cada integrante na &lt;Empresa Júnior&gt;, incluindo promoções, mudanças de cargo, troca de assessorias, projetos realizados e desligamentos.
 *   **RF06 - Registro de Avaliações e Feedbacks:** O sistema deve permitir o agendamento, preenchimento e armazenamento de avaliações de desempenho periódicas e feedbacks formais aplicados aos membros e trainees.
 *   **RF07 - Busca e Filtros Avançados:** O sistema deve fornecer uma ferramenta de busca rápida que permita filtrar a listagem de integrantes por nome, cargo, assessoria, projeto, status (ativo/inativo/trainee/alumni) e período de entrada.
 *   **RF08 - Geração de Relatórios de Gestão de Pessoas:** O sistema deve permitir a exportação de relatórios consolidados sobre o status dos membros, desempenho dos trainees, turnover e histórico de alocação em projetos em formatos legíveis (como PDF ou CSV).
@@ -754,10 +754,10 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 - Cadastro e Gestão de Membros:** O sistema deve permitir o cadastro, edição, consulta e inativação de membros da EJCM, armazenando dados pessoais, contatos, cargo ocupado, assessoria correspondente e projetos em que participa.
-*   **RF02 - Histórico de Evolução de Membros:** O sistema deve registrar e manter o histórico cronológico das movimentações de cada membro dentro da EJCM (mudanças de cargo, trocas de assessoria e participação em projetos).
+*   **RF01 - Cadastro e Gestão de Membros:** O sistema deve permitir o cadastro, edição, consulta e inativação de membros da &lt;Empresa Júnior&gt;, armazenando dados pessoais, contatos, cargo ocupado, assessoria correspondente e projetos em que participa.
+*   **RF02 - Histórico de Evolução de Membros:** O sistema deve registrar e manter o histórico cronológico das movimentações de cada membro dentro da &lt;Empresa Júnior&gt; (mudanças de cargo, trocas de assessoria e participação em projetos).
 *   **RF03 - Gestão do Processo de Trainees:** O sistema deve permitir o gerenciamento completo de trainees, incluindo o registro do cargo pretendido, controle de tarefas realizadas, notas/desempenho em treinamentos técnicos e armazenamento de feedbacks recebidos.
-*   **RF04 - Autenticação Unificada (Single Sign-On):** O sistema deve permitir o acesso unificado dos usuários utilizando uma única credencial (ex: integração com a conta institucional do Google Workspace da EJCM).
+*   **RF04 - Autenticação Unificada (Single Sign-On):** O sistema deve permitir o acesso unificado dos usuários utilizando uma única credencial (ex: integração com a conta institucional do Google Workspace da &lt;Empresa Júnior&gt;).
 *   **RF05 - Integração de Dados Externos:** O sistema deve permitir a integração e sincronização de dados atualmente armazenados em plataformas externas (como Google Planilhas, Google Drive e Notion) para evitar a duplicidade de informações.
 *   **RF06 - Controle de Permissões de Acesso:** O sistema deve possuir controle de acesso baseado em perfis (RBAC), garantindo que apenas membros da assessoria de Gestão de Pessoas possam editar dados sensíveis, feedbacks e avaliações, enquanto outros membros tenham acesso apenas para visualização ou edição de seus próprios perfis.
 *   **RF07 - Busca e Filtros Avançados:** O sistema deve disponibilizar um mecanismo de busca rápida que permita filtrar membros e trainees por nome, cargo, assessoria, projeto, status (ativo/inativo/trainee) e período de ingresso.
@@ -779,8 +779,8 @@
   <si>
     <t>### Requisitos Funcionais (RF)
 *   **RF01 - Cadastro Unificado de Membros e Trainees:** O sistema deve permitir o cadastro, edição, consulta e exclusão de dados pessoais e de contato de membros e trainees em uma única base de dados centralizada.
-*   **RF02 - Histórico de Cargos e Assessorias:** O sistema deve registrar e manter o histórico de todos os cargos ocupados, promoções e assessorias pelas quais o membro passou durante seu ciclo de vida na EJCM.
-*   **RF03 - Registro de Participação em Projetos:** O sistema deve permitir a vinculação de membros e trainees aos projetos desenvolvidos pela EJCM, registrando o papel desempenhado por cada um deles no projeto.
+*   **RF02 - Histórico de Cargos e Assessorias:** O sistema deve registrar e manter o histórico de todos os cargos ocupados, promoções e assessorias pelas quais o membro passou durante seu ciclo de vida na &lt;Empresa Júnior&gt;.
+*   **RF03 - Registro de Participação em Projetos:** O sistema deve permitir a vinculação de membros e trainees aos projetos desenvolvidos pela &lt;Empresa Júnior&gt;, registrando o papel desempenhado por cada um deles no projeto.
 *   **RF04 - Acompanhamento do Processo de Treinamento:** O sistema deve permitir o controle do progresso de capacitação dos trainees, incluindo o status de conclusão de módulos de treinamento técnico, notas e observações.
 *   **RF05 - Gerenciamento de Tarefas de Trainees:** O sistema deve permitir a atribuição, acompanhamento de prazos e registro de entrega de tarefas práticas destinadas aos trainees.
 *   **RF06 - Registro de Feedbacks e Avaliações:** O sistema deve disponibilizar um módulo para o registro e consulta de feedbacks periódicos e resultados de avaliações de desempenho de membros e trainees.
@@ -801,11 +801,11 @@
   </si>
   <si>
     <t xml:space="preserve">### Requisitos Funcionais (RF)
-*   **RF01 - Cadastro Unificado de Membros:** O sistema deve permitir o cadastro, edição, consulta e exclusão de dados pessoais e acadêmicos dos membros e trainees da EJCM.
+*   **RF01 - Cadastro Unificado de Membros:** O sistema deve permitir o cadastro, edição, consulta e exclusão de dados pessoais e acadêmicos dos membros e trainees da &lt;Empresa Júnior&gt;.
 *   **RF02 - Associação de Cargos e Assessorias:** O sistema deve permitir vincular cada membro aos seus respectivos cargos e às assessorias (departamentos) às quais pertencem.
-*   **RF03 - Registro de Participação em Projetos:** O sistema deve permitir o registro e a consulta da participação de cada membro nos projetos da EJCM, detalhando sua atuação nas etapas de Pesquisa, Prototipação, Desenvolvimento ou Entrega e Suporte.
+*   **RF03 - Registro de Participação em Projetos:** O sistema deve permitir o registro e a consulta da participação de cada membro nos projetos da &lt;Empresa Júnior&gt;, detalhando sua atuação nas etapas de Pesquisa, Prototipação, Desenvolvimento ou Entrega e Suporte.
 *   **RF04 - Acompanhamento de Trainees:** O sistema deve disponibilizar um módulo para o gerenciamento de trainees, permitindo registrar o cargo pretendido, o progresso no treinamento técnico, as tarefas realizadas e o histórico de feedbacks recebidos.
-*   **RF05 - Histórico de Movimentação de Membros:** O sistema deve registrar e manter o histórico cronológico de evolução de cada membro na EJCM, incluindo promoções, mudanças de cargo, desligamentos e avaliações de desempenho.
+*   **RF05 - Histórico de Movimentação de Membros:** O sistema deve registrar e manter o histórico cronológico de evolução de cada membro na &lt;Empresa Júnior&gt;, incluindo promoções, mudanças de cargo, desligamentos e avaliações de desempenho.
 *   **RF06 - Autenticação Unificada (Single Sign-On):** O sistema deve possuir um mecanismo de login único que permita o acesso a todas as funcionalidades de gestão de pessoas sem a necessidade de múltiplos logins.
 *   **RF07 - Controle de Acesso Baseado em Perfis:** O sistema deve permitir a atribuição de permissões de acesso diferenciadas (leitura, escrita, administração) conforme a função do usuário (ex: Assessora de GP, Diretoria, Membro, Trainee).
 *   **RF08 - Geração de Relatórios de Desempenho:** O sistema deve permitir a geração de relatórios consolidados sobre a evolução dos trainees, histórico de membros e alocação de pessoal em projetos e assessorias.
@@ -822,6 +822,9 @@
   </si>
   <si>
     <t>Omitiu completamente a LGPD e a segurança de dados sensíveis. O modelo sofreu contaminação de contexto, sugerindo gerenciar fases técnicas de projetos (RF03) e dados acadêmicos (RF01), extrapolando o escopo de GP.</t>
+  </si>
+  <si>
+    <t>93, 75</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
@@ -912,16 +915,16 @@
 Faltam mecanismos que transformem dados históricos e experiências anteriores em informações acionáveis para auxiliar o Tech Lead durante a fase de planejamento dos projetos.</t>
   </si>
   <si>
-    <t>Assessora de Vendas e Desenvolvedora Front-end da EJCM</t>
+    <t>Assessora de Vendas e Desenvolvedora Front-end da &lt;Empresa Júnior&gt;</t>
   </si>
   <si>
-    <t>Persona: “Assessora de Vendas e Desenvolvedora Front-end da EJCM”
+    <t>Persona: “Assessora de Vendas e Desenvolvedora Front-end da &lt;Empresa Júnior&gt;”
 Papel no negócio
-A Assessora de Vendas e Desenvolvedora Front-end atua em uma posição híbrida, conectando as áreas comercial e técnica da EJCM. Sua responsabilidade envolve identificar oportunidades de negócio, prospectar clientes, acompanhar o funil de vendas, organizar reuniões de diagnóstico e negociação, além de colaborar na elaboração de propostas comerciais e no desenvolvimento de soluções digitais.
+A Assessora de Vendas e Desenvolvedora Front-end atua em uma posição híbrida, conectando as áreas comercial e técnica da &lt;Empresa Júnior&gt;. Sua responsabilidade envolve identificar oportunidades de negócio, prospectar clientes, acompanhar o funil de vendas, organizar reuniões de diagnóstico e negociação, além de colaborar na elaboração de propostas comerciais e no desenvolvimento de soluções digitais.
 Sua relação com o sistema é estratégica, pois ele deve servir como uma plataforma central para gestão de leads, acompanhamento de negociações, armazenamento de conhecimento organizacional, documentação de reuniões, gerenciamento de propostas e integração entre as equipes de vendas e projetos. O sistema também deve apoiar a execução de atividades operacionais repetitivas por meio de automação, aumentando a produtividade da assessoria de vendas.
 Perfil do stakeholder
 Trata-se de uma profissional com perfil multifuncional, orientada a resultados e eficiência operacional. Demonstra forte preocupação com a produtividade da equipe comercial, a organização da informação e a redução de tarefas manuais. Possui familiaridade com ferramentas digitais e processos tecnológicos, utilizando diferentes plataformas para prospecção, comunicação, documentação e acompanhamento de vendas.
-Apresenta uma visão sistêmica dos processos da EJCM, identificando claramente os impactos que falhas de integração geram no desempenho comercial. Valoriza a centralização das informações, a automação de atividades repetitivas e a preservação do conhecimento organizacional.
+Apresenta uma visão sistêmica dos processos da &lt;Empresa Júnior&gt;, identificando claramente os impactos que falhas de integração geram no desempenho comercial. Valoriza a centralização das informações, a automação de atividades repetitivas e a preservação do conhecimento organizacional.
 Seu comportamento sugere características como:
 Organização e foco em processos;
 Orientação a metas e resultados comerciais;
@@ -941,7 +944,7 @@
 Integre informações de vendas e projetos.
 Reduza a perda de conhecimento organizacional.
 Aumente a produtividade dos assessores de vendas.
-Apoie o alcance das metas anuais da EJCM por meio de maior eficiência comercial.
+Apoie o alcance das metas anuais da &lt;Empresa Júnior&gt; por meio de maior eficiência comercial.
 Garanta segurança e proteção dos dados dos clientes.
 Necessidades explícitas
 Demandas diretamente expressas durante a entrevista:
@@ -958,7 +961,7 @@
 Gestão integrada dos dados e do conhecimento organizacional.
 Automação de processos comerciais.
 Acompanhamento do andamento dos processos de vendas.
-Operação adequada aos processos específicos da EJCM.
+Operação adequada aos processos específicos da &lt;Empresa Júnior&gt;.
 Segurança e proteção dos dados dos clientes.
 Acesso ao sistema por computadores pessoais dos membros.
 Necessidades implícitas
@@ -970,7 +973,7 @@
 Sincronização automática entre atividades comerciais e documentação.
 Controle de versionamento de propostas e documentos.
 Busca rápida por clientes, propostas e registros históricos.
-Padronização dos processos de vendas da EJCM.
+Padronização dos processos de vendas da &lt;Empresa Júnior&gt;.
 Redução da dependência de conhecimento individual dos membros.
 Facilidade de treinamento e transição de novos integrantes.
 Painéis de acompanhamento de desempenho comercial.
@@ -978,7 +981,7 @@
 Notificações e lembretes de atividades pendentes.
 Controle de acesso baseado em perfis de usuário.
 Auditoria de alterações realizadas nos dados.
-Escalabilidade para acompanhar o crescimento da EJCM.
+Escalabilidade para acompanhar o crescimento da &lt;Empresa Júnior&gt;.
 Registro estruturado de reuniões e negociações.
 Melhor colaboração entre equipes de vendas e desenvolvimento.
 Preservação do histórico institucional ao longo das gestões da empresa júnior.
@@ -1004,7 +1007,7 @@
 Atividades repetitivas consomem tempo que poderia ser dedicado à geração de novos negócios.
 Preocupação com segurança dos dados
 O tratamento de informações de clientes exige mecanismos robustos de proteção, controle de acesso e prevenção de vazamentos.
-Em síntese, esta persona representa uma profissional orientada à eficiência comercial e à integração de processos, que necessita de uma plataforma centralizada, segura e automatizada para maximizar a produtividade da equipe de vendas e preservar o conhecimento organizacional da EJCM.</t>
+Em síntese, esta persona representa uma profissional orientada à eficiência comercial e à integração de processos, que necessita de uma plataforma centralizada, segura e automatizada para maximizar a produtividade da equipe de vendas e preservar o conhecimento organizacional da &lt;Empresa Júnior&gt;.</t>
   </si>
   <si>
     <t>Assessora de Gestão de Pessoas 1</t>
@@ -1122,23 +1125,23 @@
   <si>
     <t>Persona: Assessora de Gestão de Pessoas
 Papel no negócio: -A Assessora de Gestão de Pessoas é responsável por administrar e acompanhar todo o ciclo de vida dos membros da EJCM, desde o ingresso de trainees até o acompanhamento de membros efetivos. Seu trabalho envolve o registro, atualização e consulta de informações relacionadas aos integrantes da empresa, incluindo dados pessoais, cargos ocupados, participação em assessorias e projetos, além do monitoramento do processo de treinamento, feedbacks e avaliações. O sistema exerce um papel central em sua rotina, pois deve servir como principal ferramenta para consolidar informações, reduzir tarefas operacionais e apoiar a tomada de decisão relacionada à gestão de pessoas.
+A Assessora de Gestão de Pessoas é responsável por administrar e acompanhar todo o ciclo de vida dos membros da &lt;Empresa Júnior&gt;, desde o ingresso de trainees até o acompanhamento de membros efetivos. Seu trabalho envolve o registro, atualização e consulta de informações relacionadas aos integrantes da empresa, incluindo dados pessoais, cargos ocupados, participação em assessorias e projetos, além do monitoramento do processo de treinamento, feedbacks e avaliações. O sistema exerce um papel central em sua rotina, pois deve servir como principal ferramenta para consolidar informações, reduzir tarefas operacionais e apoiar a tomada de decisão relacionada à gestão de pessoas.
 Perfil do stakeholder
 Trata-se de um perfil fortemente orientado à organização, controle de informações e eficiência operacional. Demonstra preocupação com a qualidade dos registros e com a facilidade de acesso aos dados necessários para suas atividades diárias.
 Valoriza processos simples, intuitivos e centralizados, evitando desperdício de tempo com atividades repetitivas e navegação entre diferentes plataformas. Embora reconheça que as ferramentas atuais atendam parcialmente às necessidades da assessoria, identifica claramente oportunidades de melhoria por meio da integração e da automação.
-É uma usuária frequente do sistema, principalmente em ambiente desktop, realizando consultas e atualizações diariamente. Também demonstra preocupação com a produtividade coletiva da EJCM, entendendo que a redução da carga operacional permite que os membros conciliem melhor suas atividades acadêmicas com as demandas da empresa.
+É uma usuária frequente do sistema, principalmente em ambiente desktop, realizando consultas e atualizações diariamente. Também demonstra preocupação com a produtividade coletiva da &lt;Empresa Júnior&gt;, entendendo que a redução da carga operacional permite que os membros conciliem melhor suas atividades acadêmicas com as demandas da empresa.
 Objetivos
 Centralizar todas as informações relacionadas aos membros e trainees em um único sistema.
 Eliminar a necessidade de consultar diversas plataformas para encontrar informações.
 Realizar o acompanhamento completo do processo de treinamento dos novos membros.
-Facilitar a consulta, atualização e gerenciamento dos dados dos integrantes da EJCM.
+Facilitar a consulta, atualização e gerenciamento dos dados dos integrantes da &lt;Empresa Júnior&gt;.
 Reduzir atividades manuais e repetitivas por meio da automação.
 Utilizar apenas um login para acessar todas as informações necessárias.
 Aumentar a eficiência da gestão de pessoas, especialmente durante processos seletivos, entrada de trainees e períodos de avaliação.
 Disponibilizar uma interface simples, intuitiva e de fácil utilização.
 Necessidades explícitas
 Cadastro e gerenciamento de dados pessoais dos membros.
-Registro de cargos ocupados na EJCM.
+Registro de cargos ocupados na &lt;Empresa Júnior&gt;.
 Controle das assessorias às quais cada membro pertence.
 Registro da participação em projetos.
 Gerenciamento completo dos trainees, incluindo:
@@ -1162,17 +1165,17 @@
 Histórico das movimentações e evolução dos membros ao longo do tempo.
 Padronização do armazenamento das informações.
 Atualização em tempo real dos registros.
-Controle de permissões de acesso conforme a função exercida na EJCM.
+Controle de permissões de acesso conforme a função exercida na &lt;Empresa Júnior&gt;.
 Facilidade para geração de consultas e relatórios sobre membros e trainees.
 Redução da curva de aprendizado para novos usuários do sistema.
 Elevada disponibilidade do sistema, permitindo acesso sempre que necessário.
 Interface otimizada para atividades administrativas recorrentes.
-Escalabilidade para atender diferentes assessorias da EJCM utilizando a mesma plataforma.
+Escalabilidade para atender diferentes assessorias da &lt;Empresa Júnior&gt; utilizando a mesma plataforma.
 Apoio à tomada de decisão por meio da organização das informações de gestão de pessoas.
 Principais dificuldades
 A principal dificuldade enfrentada pela Assessora de Gestão de Pessoas é a fragmentação das informações entre diversas plataformas, como Notion, Google Planilhas, Google Docs e Google Drive. Essa dispersão torna a consulta e a atualização dos dados mais lentas, aumenta o tempo gasto na execução das atividades e favorece inconsistências entre registros.
 Outro problema recorrente é a necessidade de realizar múltiplos logins e alternar constantemente entre diferentes sistemas para concluir uma única tarefa, comprometendo a produtividade e a experiência de uso.
-Além disso, processos importantes, como acompanhamento de trainees, processos seletivos e avaliações periódicas, exigem grande volume de trabalho manual e repetitivo, especialmente em momentos de maior demanda. Esse cenário reduz a eficiência operacional da assessoria e consome tempo que poderia ser direcionado às atividades estratégicas da EJCM e às responsabilidades acadêmicas dos membros.
+Além disso, processos importantes, como acompanhamento de trainees, processos seletivos e avaliações periódicas, exigem grande volume de trabalho manual e repetitivo, especialmente em momentos de maior demanda. Esse cenário reduz a eficiência operacional da assessoria e consome tempo que poderia ser direcionado às atividades estratégicas da &lt;Empresa Júnior&gt; e às responsabilidades acadêmicas dos membros.
 O sistema ideal para esse stakeholder deve mitigar esses problemas por meio da centralização das informações, integração entre ferramentas, autenticação unificada, automação de processos administrativos e disponibilização de uma interface simples, intuitiva e eficiente.</t>
   </si>
   <si>
@@ -1411,7 +1414,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="63">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1440,6 +1443,9 @@
     <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1459,7 +1465,7 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
@@ -1480,9 +1486,19 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" vertical="center"/>
     </xf>
@@ -1499,16 +1515,24 @@
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="1" fillId="5" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1519,13 +1543,22 @@
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="7" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="7" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
@@ -1708,19 +1741,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="B7:J114" displayName="Table_1" name="Table_1" id="1">
-  <tableColumns count="9">
-    <tableColumn name="Stakeholder" id="1"/>
-    <tableColumn name="Repetição" id="2"/>
-    <tableColumn name="Saída do Modelo" id="3"/>
-    <tableColumn name="Avaliação Geral" id="4"/>
-    <tableColumn name="Atendeu ao Formato" id="5"/>
-    <tableColumn name="Req. Funcionais" id="6"/>
-    <tableColumn name="Req. Não Funcionais" id="7"/>
-    <tableColumn name="Alucinações" id="8"/>
-    <tableColumn name="Observações" id="9"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="B7:K114" displayName="Table_1" name="Table_1" id="1">
+  <tableColumns count="10">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
+    <tableColumn name="Column6" id="6"/>
+    <tableColumn name="Column7" id="7"/>
+    <tableColumn name="Column8" id="8"/>
+    <tableColumn name="Column9" id="9"/>
+    <tableColumn name="Column10" id="10"/>
   </tableColumns>
   <tableStyleInfo name="Avaliação Requisitos Individuai-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <extLst>
+    <ext uri="GoogleSheetsCustomDataVersion1">
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" headerRowCount="1"/>
+    </ext>
+  </extLst>
 </table>
 </file>
 
@@ -2095,11 +2134,26 @@
       <c r="I6" s="1"/>
       <c r="J6" s="1"/>
       <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
+      <c r="L6" s="1">
+        <f t="shared" ref="L6:P6" si="1">ROUND(AVERAGE(L8:L37),2)</f>
+        <v>93.79</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="1"/>
+        <v>91.97</v>
+      </c>
+      <c r="N6" s="1">
+        <f t="shared" si="1"/>
+        <v>93.28</v>
+      </c>
+      <c r="O6" s="1">
+        <f t="shared" si="1"/>
+        <v>90.28</v>
+      </c>
+      <c r="P6" s="1">
+        <f t="shared" si="1"/>
+        <v>92.53</v>
+      </c>
       <c r="Q6" s="1"/>
       <c r="R6" s="1"/>
       <c r="S6" s="1"/>
@@ -2135,19 +2189,20 @@
       <c r="J7" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="L7" s="10" t="s">
+      <c r="K7" s="10"/>
+      <c r="L7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="M7" s="10" t="s">
+      <c r="M7" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="10" t="s">
+      <c r="N7" s="11" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="10" t="s">
+      <c r="O7" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="10" t="s">
+      <c r="P7" s="11" t="s">
         <v>17</v>
       </c>
       <c r="Q7" s="1"/>
@@ -2158,556 +2213,626 @@
     </row>
     <row r="8" ht="15.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="11" t="s">
+      <c r="B8" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="13">
         <v>1.0</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="12" t="s">
+      <c r="E8" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F8" s="12" t="s">
+      <c r="F8" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G8" s="14">
+      <c r="G8" s="15">
         <v>12.0</v>
       </c>
-      <c r="H8" s="14">
+      <c r="H8" s="15">
         <v>5.0</v>
       </c>
-      <c r="I8" s="14">
+      <c r="I8" s="15">
         <v>1.0</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="J8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K8" s="1"/>
-      <c r="L8" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M8" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="N8" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O8" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="P8" s="17">
-        <v>95.0</v>
+      <c r="K8" s="17"/>
+      <c r="L8" s="18">
+        <v>100.0</v>
+      </c>
+      <c r="M8" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="N8" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="O8" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="P8" s="18">
+        <v>100.0</v>
       </c>
       <c r="Q8" s="1"/>
       <c r="R8" s="1"/>
-      <c r="S8" s="1"/>
-      <c r="T8" s="1"/>
-      <c r="U8" s="1"/>
+      <c r="S8" s="1">
+        <f t="shared" ref="S8:S17" si="2">ROUND((T8/U8)*100,2)</f>
+        <v>94.12</v>
+      </c>
+      <c r="T8" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="U8" s="3">
+        <v>17.0</v>
+      </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="12">
+      <c r="C9" s="13">
         <v>2.0</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="12" t="s">
+      <c r="E9" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="12" t="s">
+      <c r="F9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="15">
         <v>12.0</v>
       </c>
-      <c r="H9" s="14">
+      <c r="H9" s="15">
         <v>6.0</v>
       </c>
-      <c r="I9" s="14">
+      <c r="I9" s="15">
         <v>2.0</v>
       </c>
-      <c r="J9" s="15" t="s">
+      <c r="J9" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="K9" s="1"/>
-      <c r="L9" s="16">
-        <v>92.0</v>
-      </c>
-      <c r="M9" s="17">
-        <v>92.0</v>
-      </c>
-      <c r="N9" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O9" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="P9" s="17">
-        <v>96.0</v>
+      <c r="K9" s="17"/>
+      <c r="L9" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="M9" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N9" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O9" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="P9" s="18">
+        <v>94.44</v>
       </c>
       <c r="Q9" s="1"/>
       <c r="R9" s="1"/>
-      <c r="S9" s="1"/>
-      <c r="T9" s="1"/>
-      <c r="U9" s="1"/>
+      <c r="S9" s="1">
+        <f t="shared" si="2"/>
+        <v>88.89</v>
+      </c>
+      <c r="T9" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="U9" s="3">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="13">
         <v>3.0</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="12" t="s">
+      <c r="E10" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F10" s="12" t="s">
+      <c r="F10" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G10" s="14">
+      <c r="G10" s="15">
         <v>12.0</v>
       </c>
-      <c r="H10" s="14">
+      <c r="H10" s="15">
         <v>6.0</v>
       </c>
-      <c r="I10" s="14">
+      <c r="I10" s="15">
         <v>3.0</v>
       </c>
-      <c r="J10" s="15" t="s">
+      <c r="J10" s="16" t="s">
         <v>27</v>
       </c>
-      <c r="K10" s="1"/>
-      <c r="L10" s="16">
-        <v>85.0</v>
-      </c>
-      <c r="M10" s="17">
-        <v>88.0</v>
-      </c>
-      <c r="N10" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O10" s="17">
-        <v>83.0</v>
-      </c>
-      <c r="P10" s="17">
-        <v>89.0</v>
+      <c r="K10" s="17"/>
+      <c r="L10" s="3">
+        <v>83.33</v>
+      </c>
+      <c r="M10" s="18">
+        <v>88.89</v>
+      </c>
+      <c r="N10" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O10" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="P10" s="18">
+        <v>88.89</v>
       </c>
       <c r="Q10" s="1"/>
       <c r="R10" s="1"/>
-      <c r="S10" s="1"/>
-      <c r="T10" s="1"/>
-      <c r="U10" s="1"/>
+      <c r="S10" s="1">
+        <f t="shared" si="2"/>
+        <v>88.89</v>
+      </c>
+      <c r="T10" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="U10" s="3">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="11" t="s">
+      <c r="B11" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="12">
+      <c r="C11" s="13">
         <v>4.0</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E11" s="12" t="s">
+      <c r="E11" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="12" t="s">
+      <c r="F11" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="14">
+      <c r="G11" s="15">
         <v>12.0</v>
       </c>
-      <c r="H11" s="14">
+      <c r="H11" s="15">
         <v>6.0</v>
       </c>
-      <c r="I11" s="14">
+      <c r="I11" s="15">
         <v>1.0</v>
       </c>
-      <c r="J11" s="15" t="s">
+      <c r="J11" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="1"/>
-      <c r="L11" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M11" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="N11" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="O11" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="P11" s="17">
-        <v>95.0</v>
+      <c r="K11" s="17"/>
+      <c r="L11" s="18">
+        <v>100.0</v>
+      </c>
+      <c r="M11" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N11" s="3">
+        <v>88.89</v>
+      </c>
+      <c r="O11" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="P11" s="18">
+        <v>94.44</v>
       </c>
       <c r="Q11" s="1"/>
       <c r="R11" s="1"/>
-      <c r="S11" s="1"/>
-      <c r="T11" s="1"/>
-      <c r="U11" s="1"/>
+      <c r="S11" s="1">
+        <f t="shared" si="2"/>
+        <v>94.44</v>
+      </c>
+      <c r="T11" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="U11" s="3">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="19">
+      <c r="C12" s="20">
         <v>5.0</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="22">
         <v>12.0</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="22">
         <v>7.0</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="22">
         <v>1.0</v>
       </c>
-      <c r="J12" s="22" t="s">
+      <c r="J12" s="23" t="s">
         <v>31</v>
       </c>
-      <c r="K12" s="1"/>
-      <c r="L12" s="23">
-        <v>97.0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>99.0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>97.0</v>
+      <c r="K12" s="24"/>
+      <c r="L12" s="25">
+        <v>100.0</v>
+      </c>
+      <c r="M12" s="25">
+        <v>100.0</v>
+      </c>
+      <c r="N12" s="25">
+        <v>94.74</v>
+      </c>
+      <c r="O12" s="25">
+        <v>94.74</v>
+      </c>
+      <c r="P12" s="25">
+        <v>94.74</v>
       </c>
       <c r="Q12" s="1"/>
       <c r="R12" s="1"/>
-      <c r="S12" s="1"/>
-      <c r="T12" s="1"/>
-      <c r="U12" s="1"/>
+      <c r="S12" s="1">
+        <f t="shared" si="2"/>
+        <v>94.74</v>
+      </c>
+      <c r="T12" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="U12" s="3">
+        <v>19.0</v>
+      </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="11" t="s">
+      <c r="B13" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="12">
+      <c r="C13" s="13">
         <v>1.0</v>
       </c>
-      <c r="D13" s="13" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="12" t="s">
+      <c r="E13" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="12" t="s">
+      <c r="F13" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G13" s="14">
+      <c r="G13" s="15">
         <v>11.0</v>
       </c>
-      <c r="H13" s="14">
+      <c r="H13" s="15">
         <v>6.0</v>
       </c>
-      <c r="I13" s="14">
+      <c r="I13" s="15">
         <v>0.0</v>
       </c>
-      <c r="J13" s="15" t="s">
+      <c r="J13" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="K13" s="1"/>
-      <c r="L13" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M13" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="N13" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="O13" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="P13" s="17">
-        <v>95.0</v>
+      <c r="K13" s="17"/>
+      <c r="L13" s="26">
+        <v>100.0</v>
+      </c>
+      <c r="M13" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="N13" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="O13" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="P13" s="18">
+        <v>88.24</v>
       </c>
       <c r="Q13" s="1"/>
       <c r="R13" s="1"/>
-      <c r="S13" s="1"/>
-      <c r="T13" s="1"/>
-      <c r="U13" s="1"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="24"/>
-      <c r="B14" s="25" t="s">
+      <c r="S13" s="27">
+        <f t="shared" si="2"/>
+        <v>88.24</v>
+      </c>
+      <c r="T13" s="28">
+        <v>15.0</v>
+      </c>
+      <c r="U13" s="28">
+        <v>17.0</v>
+      </c>
+    </row>
+    <row r="14" ht="15.0" customHeight="1">
+      <c r="A14" s="29"/>
+      <c r="B14" s="30" t="s">
         <v>35</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="31">
         <v>2.0</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="32" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="26" t="s">
+      <c r="E14" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="F14" s="26" t="s">
+      <c r="F14" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="33">
         <v>14.0</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="33">
         <v>7.0</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="33">
         <v>0.0</v>
       </c>
-      <c r="J14" s="29" t="s">
+      <c r="J14" s="34" t="s">
         <v>37</v>
       </c>
-      <c r="K14" s="24"/>
-      <c r="L14" s="30">
-        <v>97.0</v>
-      </c>
-      <c r="M14" s="31">
-        <v>97.0</v>
-      </c>
-      <c r="N14" s="31">
-        <v>96.0</v>
-      </c>
-      <c r="O14" s="31">
-        <v>95.0</v>
-      </c>
-      <c r="P14" s="31">
-        <v>96.0</v>
+      <c r="K14" s="35"/>
+      <c r="L14" s="36">
+        <v>100.0</v>
+      </c>
+      <c r="M14" s="36">
+        <v>95.24</v>
+      </c>
+      <c r="N14" s="37">
+        <v>90.48</v>
+      </c>
+      <c r="O14" s="37">
+        <v>90.48</v>
+      </c>
+      <c r="P14" s="36">
+        <v>95.24</v>
       </c>
       <c r="Q14" s="1"/>
-      <c r="R14" s="24"/>
-      <c r="S14" s="24"/>
-      <c r="T14" s="24"/>
-      <c r="U14" s="24"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="29">
+        <f t="shared" si="2"/>
+        <v>95.24</v>
+      </c>
+      <c r="T14" s="37">
+        <v>20.0</v>
+      </c>
+      <c r="U14" s="37">
+        <v>21.0</v>
+      </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="11" t="s">
+      <c r="B15" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="12">
+      <c r="C15" s="13">
         <v>3.0</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="E15" s="12" t="s">
+      <c r="E15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F15" s="12" t="s">
+      <c r="F15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G15" s="14">
+      <c r="G15" s="15">
         <v>13.0</v>
       </c>
-      <c r="H15" s="14">
+      <c r="H15" s="15">
         <v>5.0</v>
       </c>
-      <c r="I15" s="14">
+      <c r="I15" s="15">
         <v>0.0</v>
       </c>
-      <c r="J15" s="15" t="s">
+      <c r="J15" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="K15" s="1"/>
-      <c r="L15" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>97.0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>97.0</v>
+      <c r="K15" s="17"/>
+      <c r="L15" s="26">
+        <v>100.0</v>
+      </c>
+      <c r="M15" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N15" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O15" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="P15" s="18">
+        <v>94.44</v>
       </c>
       <c r="Q15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="1"/>
-      <c r="T15" s="1"/>
-      <c r="U15" s="1"/>
+      <c r="S15" s="27">
+        <f t="shared" si="2"/>
+        <v>94.44</v>
+      </c>
+      <c r="T15" s="28">
+        <v>17.0</v>
+      </c>
+      <c r="U15" s="28">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="11" t="s">
+      <c r="B16" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="13">
         <v>4.0</v>
       </c>
-      <c r="D16" s="13" t="s">
+      <c r="D16" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="E16" s="12" t="s">
+      <c r="E16" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="12" t="s">
+      <c r="F16" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G16" s="14">
+      <c r="G16" s="15">
         <v>12.0</v>
       </c>
-      <c r="H16" s="14">
+      <c r="H16" s="15">
         <v>5.0</v>
       </c>
-      <c r="I16" s="14">
+      <c r="I16" s="15">
         <v>0.0</v>
       </c>
-      <c r="J16" s="15" t="s">
+      <c r="J16" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="K16" s="1"/>
-      <c r="L16" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M16" s="17">
-        <v>97.0</v>
-      </c>
-      <c r="N16" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O16" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="P16" s="17">
-        <v>94.0</v>
+      <c r="K16" s="17"/>
+      <c r="L16" s="26">
+        <v>100.0</v>
+      </c>
+      <c r="M16" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="N16" s="18">
+        <v>100.0</v>
+      </c>
+      <c r="O16" s="18">
+        <v>100.0</v>
+      </c>
+      <c r="P16" s="18">
+        <v>94.12</v>
       </c>
       <c r="Q16" s="1"/>
       <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
-      <c r="U16" s="1"/>
+      <c r="S16" s="27">
+        <f t="shared" si="2"/>
+        <v>94.12</v>
+      </c>
+      <c r="T16" s="28">
+        <v>16.0</v>
+      </c>
+      <c r="U16" s="28">
+        <v>17.0</v>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="11" t="s">
+      <c r="B17" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="12">
+      <c r="C17" s="13">
         <v>5.0</v>
       </c>
-      <c r="D17" s="13" t="s">
+      <c r="D17" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E17" s="12" t="s">
+      <c r="E17" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F17" s="12" t="s">
+      <c r="F17" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G17" s="14">
+      <c r="G17" s="15">
         <v>12.0</v>
       </c>
-      <c r="H17" s="14">
+      <c r="H17" s="15">
         <v>6.0</v>
       </c>
-      <c r="I17" s="14">
+      <c r="I17" s="15">
         <v>0.0</v>
       </c>
-      <c r="J17" s="15" t="s">
+      <c r="J17" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="K17" s="1"/>
-      <c r="L17" s="16">
-        <v>93.0</v>
-      </c>
-      <c r="M17" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="N17" s="17">
-        <v>92.0</v>
-      </c>
-      <c r="O17" s="17">
-        <v>89.0</v>
-      </c>
-      <c r="P17" s="17">
-        <v>94.0</v>
+      <c r="K17" s="17"/>
+      <c r="L17" s="26">
+        <v>94.44</v>
+      </c>
+      <c r="M17" s="18">
+        <v>88.89</v>
+      </c>
+      <c r="N17" s="18">
+        <v>88.89</v>
+      </c>
+      <c r="O17" s="26">
+        <v>94.44</v>
+      </c>
+      <c r="P17" s="26">
+        <v>94.44</v>
       </c>
       <c r="Q17" s="1"/>
       <c r="R17" s="1"/>
-      <c r="S17" s="1"/>
-      <c r="T17" s="1"/>
-      <c r="U17" s="1"/>
+      <c r="S17" s="27">
+        <f t="shared" si="2"/>
+        <v>94.44</v>
+      </c>
+      <c r="T17" s="28">
+        <v>17.0</v>
+      </c>
+      <c r="U17" s="28">
+        <v>18.0</v>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="11" t="s">
+      <c r="B18" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="13">
         <v>1.0</v>
       </c>
-      <c r="D18" s="13" t="s">
+      <c r="D18" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="E18" s="12" t="s">
+      <c r="E18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="12" t="s">
+      <c r="F18" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G18" s="14">
+      <c r="G18" s="15">
         <v>11.0</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="15">
         <v>7.0</v>
       </c>
-      <c r="I18" s="14">
+      <c r="I18" s="15">
         <v>0.0</v>
       </c>
-      <c r="J18" s="15"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="16">
-        <v>83.0</v>
-      </c>
-      <c r="M18" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="N18" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O18" s="17">
-        <v>83.0</v>
-      </c>
-      <c r="P18" s="17">
-        <v>83.0</v>
+      <c r="J18" s="16"/>
+      <c r="K18" s="17"/>
+      <c r="L18" s="26">
+        <v>83.33</v>
+      </c>
+      <c r="M18" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N18" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O18" s="18">
+        <v>83.33</v>
+      </c>
+      <c r="P18" s="18">
+        <v>83.33</v>
       </c>
       <c r="Q18" s="1"/>
       <c r="R18" s="1"/>
@@ -2717,48 +2842,48 @@
     </row>
     <row r="19" ht="15.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="11" t="s">
+      <c r="B19" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="12">
+      <c r="C19" s="13">
         <v>2.0</v>
       </c>
-      <c r="D19" s="13" t="s">
+      <c r="D19" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E19" s="12" t="s">
+      <c r="E19" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F19" s="12" t="s">
+      <c r="F19" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G19" s="14">
+      <c r="G19" s="15">
         <v>12.0</v>
       </c>
-      <c r="H19" s="14">
+      <c r="H19" s="15">
         <v>6.0</v>
       </c>
-      <c r="I19" s="14">
+      <c r="I19" s="15">
         <v>0.0</v>
       </c>
-      <c r="J19" s="15" t="s">
+      <c r="J19" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="K19" s="1"/>
-      <c r="L19" s="16">
-        <v>89.0</v>
-      </c>
-      <c r="M19" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="N19" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O19" s="17">
-        <v>89.0</v>
-      </c>
-      <c r="P19" s="17">
-        <v>89.0</v>
+      <c r="K19" s="17"/>
+      <c r="L19" s="26">
+        <v>88.88</v>
+      </c>
+      <c r="M19" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N19" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O19" s="18">
+        <v>88.88</v>
+      </c>
+      <c r="P19" s="18">
+        <v>88.88</v>
       </c>
       <c r="Q19" s="1"/>
       <c r="R19" s="1"/>
@@ -2768,48 +2893,48 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="11" t="s">
+      <c r="B20" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="13">
         <v>3.0</v>
       </c>
-      <c r="D20" s="13" t="s">
+      <c r="D20" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="E20" s="12" t="s">
+      <c r="E20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G20" s="14">
+      <c r="G20" s="15">
         <v>11.0</v>
       </c>
-      <c r="H20" s="14">
+      <c r="H20" s="15">
         <v>6.0</v>
       </c>
-      <c r="I20" s="14">
+      <c r="I20" s="15">
         <v>0.0</v>
       </c>
-      <c r="J20" s="15" t="s">
+      <c r="J20" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="K20" s="1"/>
-      <c r="L20" s="16">
-        <v>82.0</v>
-      </c>
-      <c r="M20" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="N20" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O20" s="17">
-        <v>88.0</v>
-      </c>
-      <c r="P20" s="17">
-        <v>94.0</v>
+      <c r="K20" s="17"/>
+      <c r="L20" s="26">
+        <v>82.35</v>
+      </c>
+      <c r="M20" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="N20" s="18">
+        <v>94.12</v>
+      </c>
+      <c r="O20" s="18">
+        <v>88.23</v>
+      </c>
+      <c r="P20" s="18">
+        <v>94.12</v>
       </c>
       <c r="Q20" s="1"/>
       <c r="R20" s="1"/>
@@ -2819,97 +2944,99 @@
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="C21" s="12">
+      <c r="C21" s="20">
         <v>4.0</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="12" t="s">
+      <c r="E21" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G21" s="14">
+      <c r="G21" s="22">
         <v>12.0</v>
       </c>
-      <c r="H21" s="14">
+      <c r="H21" s="22">
         <v>7.0</v>
       </c>
-      <c r="I21" s="14">
+      <c r="I21" s="22">
         <v>1.0</v>
       </c>
-      <c r="J21" s="15" t="s">
+      <c r="J21" s="23" t="s">
         <v>52</v>
       </c>
-      <c r="K21" s="1"/>
-      <c r="L21" s="16">
-        <v>95.0</v>
-      </c>
-      <c r="M21" s="17">
+      <c r="K21" s="24"/>
+      <c r="L21" s="38">
+        <v>94.74</v>
+      </c>
+      <c r="M21" s="25">
         <v>100.0</v>
       </c>
-      <c r="N21" s="17">
-        <v>89.0</v>
-      </c>
-      <c r="O21" s="17">
-        <v>89.0</v>
-      </c>
-      <c r="P21" s="17">
-        <v>89.0</v>
-      </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1"/>
-      <c r="U21" s="1"/>
+      <c r="N21" s="25">
+        <v>89.47</v>
+      </c>
+      <c r="O21" s="25">
+        <v>89.47</v>
+      </c>
+      <c r="P21" s="25">
+        <v>89.47</v>
+      </c>
+      <c r="Q21" s="39"/>
+      <c r="R21" s="39"/>
+      <c r="S21" s="39"/>
+      <c r="T21" s="39"/>
+      <c r="U21" s="3">
+        <v>19.0</v>
+      </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="C22" s="12">
+      <c r="C22" s="13">
         <v>5.0</v>
       </c>
-      <c r="D22" s="13" t="s">
+      <c r="D22" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="E22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G22" s="14">
+      <c r="G22" s="15">
         <v>11.0</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="15">
         <v>7.0</v>
       </c>
-      <c r="I22" s="14">
+      <c r="I22" s="15">
         <v>0.0</v>
       </c>
-      <c r="J22" s="32"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="16">
-        <v>94.0</v>
-      </c>
-      <c r="M22" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="N22" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O22" s="17">
-        <v>83.0</v>
-      </c>
-      <c r="P22" s="17">
-        <v>83.3</v>
+      <c r="J22" s="40"/>
+      <c r="K22" s="40"/>
+      <c r="L22" s="26">
+        <v>94.44</v>
+      </c>
+      <c r="M22" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="N22" s="18">
+        <v>94.44</v>
+      </c>
+      <c r="O22" s="18">
+        <v>83.33</v>
+      </c>
+      <c r="P22" s="18">
+        <v>83.33</v>
       </c>
       <c r="Q22" s="1"/>
       <c r="R22" s="1"/>
@@ -2919,303 +3046,303 @@
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="19" t="s">
         <v>54</v>
       </c>
-      <c r="C23" s="19">
+      <c r="C23" s="20">
         <v>1.0</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="E23" s="19" t="s">
+      <c r="E23" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F23" s="19" t="s">
+      <c r="F23" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="22">
         <v>10.0</v>
       </c>
-      <c r="H23" s="21">
+      <c r="H23" s="22">
         <v>5.0</v>
       </c>
-      <c r="I23" s="21">
+      <c r="I23" s="22">
         <v>0.0</v>
       </c>
-      <c r="J23" s="22" t="s">
+      <c r="J23" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="K23" s="1"/>
-      <c r="L23" s="23">
-        <v>95.0</v>
-      </c>
-      <c r="M23" s="17">
-        <v>90.0</v>
-      </c>
-      <c r="N23" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O23" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="P23" s="17">
-        <v>95.0</v>
+      <c r="K23" s="23"/>
+      <c r="L23" s="38">
+        <v>93.33</v>
+      </c>
+      <c r="M23" s="18">
+        <v>86.67</v>
+      </c>
+      <c r="N23" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="O23" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="P23" s="18">
+        <v>93.33</v>
       </c>
       <c r="Q23" s="1"/>
       <c r="R23" s="1"/>
       <c r="S23" s="1"/>
-      <c r="T23" s="1"/>
-      <c r="U23" s="1"/>
+      <c r="T23" s="3"/>
+      <c r="U23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="12">
+      <c r="C24" s="13">
         <v>2.0</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="D24" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="E24" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G24" s="14">
+      <c r="G24" s="15">
         <v>10.0</v>
       </c>
-      <c r="H24" s="14">
+      <c r="H24" s="15">
         <v>5.0</v>
       </c>
-      <c r="I24" s="14">
+      <c r="I24" s="15">
         <v>0.0</v>
       </c>
-      <c r="J24" s="15" t="s">
+      <c r="J24" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="K24" s="1"/>
-      <c r="L24" s="16">
-        <v>98.0</v>
-      </c>
-      <c r="M24" s="17">
-        <v>99.0</v>
-      </c>
-      <c r="N24" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="O24" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="P24" s="17">
-        <v>98.0</v>
+      <c r="K24" s="16"/>
+      <c r="L24" s="26">
+        <v>100.0</v>
+      </c>
+      <c r="M24" s="18">
+        <v>100.0</v>
+      </c>
+      <c r="N24" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="O24" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="P24" s="18">
+        <v>100.0</v>
       </c>
       <c r="Q24" s="1"/>
       <c r="R24" s="1"/>
       <c r="S24" s="1"/>
-      <c r="T24" s="1"/>
-      <c r="U24" s="1"/>
+      <c r="T24" s="3"/>
+      <c r="U24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="11" t="s">
+      <c r="B25" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C25" s="12">
+      <c r="C25" s="13">
         <v>3.0</v>
       </c>
-      <c r="D25" s="13" t="s">
+      <c r="D25" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="E25" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G25" s="14">
+      <c r="G25" s="15">
         <v>9.0</v>
       </c>
-      <c r="H25" s="14">
+      <c r="H25" s="15">
         <v>5.0</v>
       </c>
-      <c r="I25" s="14">
+      <c r="I25" s="15">
         <v>1.0</v>
       </c>
-      <c r="J25" s="15" t="s">
+      <c r="J25" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="K25" s="1"/>
-      <c r="L25" s="16">
-        <v>92.0</v>
-      </c>
-      <c r="M25" s="17">
-        <v>80.0</v>
-      </c>
-      <c r="N25" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O25" s="17">
-        <v>85.0</v>
-      </c>
-      <c r="P25" s="17">
-        <v>90.0</v>
+      <c r="K25" s="17"/>
+      <c r="L25" s="26">
+        <v>92.86</v>
+      </c>
+      <c r="M25" s="18">
+        <v>78.57</v>
+      </c>
+      <c r="N25" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O25" s="18">
+        <v>85.71</v>
+      </c>
+      <c r="P25" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q25" s="1"/>
       <c r="R25" s="1"/>
       <c r="S25" s="1"/>
-      <c r="T25" s="1"/>
-      <c r="U25" s="1"/>
+      <c r="T25" s="3"/>
+      <c r="U25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="11" t="s">
+      <c r="B26" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="12">
+      <c r="C26" s="13">
         <v>4.0</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="D26" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E26" s="12" t="s">
+      <c r="E26" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G26" s="14">
+      <c r="G26" s="15">
         <v>10.0</v>
       </c>
-      <c r="H26" s="14">
+      <c r="H26" s="15">
         <v>5.0</v>
       </c>
-      <c r="I26" s="14">
+      <c r="I26" s="15">
         <v>0.0</v>
       </c>
-      <c r="J26" s="15" t="s">
+      <c r="J26" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="K26" s="1"/>
-      <c r="L26" s="16">
-        <v>95.0</v>
-      </c>
-      <c r="M26" s="17">
-        <v>91.0</v>
-      </c>
-      <c r="N26" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O26" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="P26" s="17">
-        <v>95.0</v>
+      <c r="K26" s="17"/>
+      <c r="L26" s="26">
+        <v>93.33</v>
+      </c>
+      <c r="M26" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="N26" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="O26" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="P26" s="18">
+        <v>93.33</v>
       </c>
       <c r="Q26" s="1"/>
       <c r="R26" s="1"/>
       <c r="S26" s="1"/>
-      <c r="T26" s="1"/>
-      <c r="U26" s="1"/>
+      <c r="T26" s="3"/>
+      <c r="U26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="11" t="s">
+      <c r="B27" s="12" t="s">
         <v>54</v>
       </c>
-      <c r="C27" s="12">
+      <c r="C27" s="13">
         <v>5.0</v>
       </c>
-      <c r="D27" s="13" t="s">
+      <c r="D27" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="12" t="s">
+      <c r="E27" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G27" s="14">
+      <c r="G27" s="15">
         <v>9.0</v>
       </c>
-      <c r="H27" s="14">
+      <c r="H27" s="15">
         <v>4.0</v>
       </c>
-      <c r="I27" s="14">
+      <c r="I27" s="15">
         <v>0.0</v>
       </c>
-      <c r="J27" s="15" t="s">
+      <c r="J27" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="K27" s="1"/>
-      <c r="L27" s="16">
-        <v>93.0</v>
-      </c>
-      <c r="M27" s="17">
-        <v>85.0</v>
-      </c>
-      <c r="N27" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O27" s="17">
-        <v>88.0</v>
-      </c>
-      <c r="P27" s="17">
-        <v>93.0</v>
+      <c r="K27" s="17"/>
+      <c r="L27" s="26">
+        <v>92.31</v>
+      </c>
+      <c r="M27" s="18">
+        <v>84.62</v>
+      </c>
+      <c r="N27" s="18">
+        <v>92.31</v>
+      </c>
+      <c r="O27" s="18">
+        <v>84.62</v>
+      </c>
+      <c r="P27" s="18">
+        <v>92.31</v>
       </c>
       <c r="Q27" s="1"/>
       <c r="R27" s="1"/>
       <c r="S27" s="1"/>
-      <c r="T27" s="1"/>
-      <c r="U27" s="1"/>
+      <c r="T27" s="3"/>
+      <c r="U27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="11" t="s">
+      <c r="B28" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C28" s="12">
+      <c r="C28" s="13">
         <v>1.0</v>
       </c>
-      <c r="D28" s="13" t="s">
+      <c r="D28" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="E28" s="12" t="s">
+      <c r="E28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G28" s="14">
+      <c r="G28" s="15">
         <v>10.0</v>
       </c>
-      <c r="H28" s="14">
+      <c r="H28" s="15">
         <v>4.0</v>
       </c>
-      <c r="I28" s="14">
+      <c r="I28" s="15">
         <v>0.0</v>
       </c>
-      <c r="J28" s="15" t="s">
+      <c r="J28" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="K28" s="1"/>
-      <c r="L28" s="16">
-        <v>97.0</v>
-      </c>
-      <c r="M28" s="17">
-        <v>98.0</v>
-      </c>
-      <c r="N28" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="O28" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="P28" s="17">
-        <v>96.0</v>
+      <c r="K28" s="17"/>
+      <c r="L28" s="26">
+        <v>92.86</v>
+      </c>
+      <c r="M28" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="N28" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O28" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="P28" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q28" s="1"/>
       <c r="R28" s="1"/>
@@ -3225,48 +3352,48 @@
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="11" t="s">
+      <c r="B29" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C29" s="12">
+      <c r="C29" s="13">
         <v>2.0</v>
       </c>
-      <c r="D29" s="13" t="s">
+      <c r="D29" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="12" t="s">
+      <c r="E29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F29" s="12" t="s">
+      <c r="F29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G29" s="14">
+      <c r="G29" s="15">
         <v>10.0</v>
       </c>
-      <c r="H29" s="14">
+      <c r="H29" s="15">
         <v>4.0</v>
       </c>
-      <c r="I29" s="14">
+      <c r="I29" s="15">
         <v>0.0</v>
       </c>
-      <c r="J29" s="15" t="s">
+      <c r="J29" s="16" t="s">
         <v>69</v>
       </c>
-      <c r="K29" s="1"/>
-      <c r="L29" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M29" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="N29" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O29" s="17">
-        <v>92.0</v>
-      </c>
-      <c r="P29" s="17">
-        <v>95.0</v>
+      <c r="K29" s="17"/>
+      <c r="L29" s="26">
+        <v>92.86</v>
+      </c>
+      <c r="M29" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="N29" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O29" s="18">
+        <v>85.71</v>
+      </c>
+      <c r="P29" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q29" s="1"/>
       <c r="R29" s="1"/>
@@ -3276,48 +3403,48 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="11" t="s">
+      <c r="B30" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C30" s="12">
+      <c r="C30" s="13">
         <v>3.0</v>
       </c>
-      <c r="D30" s="13" t="s">
+      <c r="D30" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="12" t="s">
+      <c r="E30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F30" s="12" t="s">
+      <c r="F30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G30" s="14">
+      <c r="G30" s="15">
         <v>10.0</v>
       </c>
-      <c r="H30" s="14">
+      <c r="H30" s="15">
         <v>4.0</v>
       </c>
-      <c r="I30" s="14">
+      <c r="I30" s="15">
         <v>0.0</v>
       </c>
-      <c r="J30" s="15" t="s">
+      <c r="J30" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="K30" s="1"/>
-      <c r="L30" s="16">
-        <v>96.0</v>
-      </c>
-      <c r="M30" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="N30" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O30" s="17">
-        <v>97.0</v>
-      </c>
-      <c r="P30" s="17">
-        <v>96.0</v>
+      <c r="K30" s="17"/>
+      <c r="L30" s="26">
+        <v>92.86</v>
+      </c>
+      <c r="M30" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="N30" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O30" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="P30" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q30" s="1"/>
       <c r="R30" s="1"/>
@@ -3326,100 +3453,100 @@
       <c r="U30" s="1"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="33"/>
-      <c r="B31" s="18" t="s">
+      <c r="A31" s="39"/>
+      <c r="B31" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="C31" s="19">
+      <c r="C31" s="20">
         <v>4.0</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="21" t="s">
         <v>72</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F31" s="19" t="s">
+      <c r="F31" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="G31" s="21">
+      <c r="G31" s="22">
         <v>10.0</v>
       </c>
-      <c r="H31" s="21">
+      <c r="H31" s="22">
         <v>5.0</v>
       </c>
-      <c r="I31" s="21">
+      <c r="I31" s="22">
         <v>0.0</v>
       </c>
-      <c r="J31" s="22" t="s">
+      <c r="J31" s="23" t="s">
         <v>73</v>
       </c>
-      <c r="K31" s="34"/>
-      <c r="L31" s="35">
-        <v>97.0</v>
-      </c>
-      <c r="M31" s="36">
-        <v>97.0</v>
-      </c>
-      <c r="N31" s="36">
-        <v>96.0</v>
-      </c>
-      <c r="O31" s="36">
-        <v>96.0</v>
-      </c>
-      <c r="P31" s="36">
-        <v>98.0</v>
+      <c r="K31" s="41"/>
+      <c r="L31" s="42">
+        <v>93.33</v>
+      </c>
+      <c r="M31" s="43">
+        <v>93.33</v>
+      </c>
+      <c r="N31" s="43">
+        <v>93.33</v>
+      </c>
+      <c r="O31" s="43">
+        <v>93.33</v>
+      </c>
+      <c r="P31" s="43">
+        <v>93.33</v>
       </c>
       <c r="Q31" s="1"/>
-      <c r="R31" s="33"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="33"/>
-      <c r="U31" s="33"/>
+      <c r="R31" s="39"/>
+      <c r="S31" s="39"/>
+      <c r="T31" s="39"/>
+      <c r="U31" s="39"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="11" t="s">
+      <c r="B32" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="C32" s="12">
+      <c r="C32" s="13">
         <v>5.0</v>
       </c>
-      <c r="D32" s="13" t="s">
+      <c r="D32" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="E32" s="12" t="s">
+      <c r="E32" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F32" s="12" t="s">
+      <c r="F32" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G32" s="14">
+      <c r="G32" s="15">
         <v>10.0</v>
       </c>
-      <c r="H32" s="14">
+      <c r="H32" s="15">
         <v>4.0</v>
       </c>
-      <c r="I32" s="14">
+      <c r="I32" s="15">
         <v>0.0</v>
       </c>
-      <c r="J32" s="15" t="s">
+      <c r="J32" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="K32" s="1"/>
-      <c r="L32" s="16">
-        <v>97.0</v>
-      </c>
-      <c r="M32" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="N32" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O32" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="P32" s="17">
-        <v>97.0</v>
+      <c r="K32" s="17"/>
+      <c r="L32" s="26">
+        <v>92.86</v>
+      </c>
+      <c r="M32" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="N32" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O32" s="18">
+        <v>85.71</v>
+      </c>
+      <c r="P32" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q32" s="1"/>
       <c r="R32" s="1"/>
@@ -3429,48 +3556,48 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="11" t="s">
+      <c r="B33" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="12">
+      <c r="C33" s="13">
         <v>1.0</v>
       </c>
-      <c r="D33" s="13" t="s">
+      <c r="D33" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="12" t="s">
+      <c r="E33" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F33" s="12" t="s">
+      <c r="F33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G33" s="14">
+      <c r="G33" s="15">
         <v>8.0</v>
       </c>
-      <c r="H33" s="14">
+      <c r="H33" s="15">
         <v>6.0</v>
       </c>
-      <c r="I33" s="14">
+      <c r="I33" s="15">
         <v>1.0</v>
       </c>
-      <c r="J33" s="37" t="s">
+      <c r="J33" s="44" t="s">
         <v>78</v>
       </c>
-      <c r="K33" s="1"/>
-      <c r="L33" s="38">
-        <v>96.0</v>
-      </c>
-      <c r="M33" s="17">
-        <v>88.0</v>
-      </c>
-      <c r="N33" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O33" s="17">
-        <v>86.0</v>
-      </c>
-      <c r="P33" s="17">
-        <v>95.0</v>
+      <c r="K33" s="45"/>
+      <c r="L33" s="46">
+        <v>92.86</v>
+      </c>
+      <c r="M33" s="18">
+        <v>85.71</v>
+      </c>
+      <c r="N33" s="18">
+        <v>92.86</v>
+      </c>
+      <c r="O33" s="18">
+        <v>85.71</v>
+      </c>
+      <c r="P33" s="18">
+        <v>92.86</v>
       </c>
       <c r="Q33" s="1"/>
       <c r="R33" s="1"/>
@@ -3480,48 +3607,48 @@
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="C34" s="19">
+      <c r="C34" s="20">
         <v>2.0</v>
       </c>
-      <c r="D34" s="20" t="s">
+      <c r="D34" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="E34" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="F34" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="22">
         <v>10.0</v>
       </c>
-      <c r="H34" s="21">
+      <c r="H34" s="22">
         <v>6.0</v>
       </c>
-      <c r="I34" s="21">
+      <c r="I34" s="22">
         <v>0.0</v>
       </c>
-      <c r="J34" s="39" t="s">
+      <c r="J34" s="47" t="s">
         <v>80</v>
       </c>
-      <c r="K34" s="1"/>
-      <c r="L34" s="40">
-        <v>98.0</v>
-      </c>
-      <c r="M34" s="17">
-        <v>99.0</v>
-      </c>
-      <c r="N34" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="O34" s="17">
-        <v>98.0</v>
-      </c>
-      <c r="P34" s="17">
-        <v>97.0</v>
+      <c r="K34" s="48"/>
+      <c r="L34" s="49">
+        <v>93.75</v>
+      </c>
+      <c r="M34" s="18">
+        <v>93.75</v>
+      </c>
+      <c r="N34" s="18">
+        <v>93.75</v>
+      </c>
+      <c r="O34" s="18">
+        <v>93.75</v>
+      </c>
+      <c r="P34" s="18">
+        <v>93.75</v>
       </c>
       <c r="Q34" s="1"/>
       <c r="R34" s="1"/>
@@ -3531,48 +3658,48 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="12">
+      <c r="C35" s="13">
         <v>3.0</v>
       </c>
-      <c r="D35" s="13" t="s">
+      <c r="D35" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="12" t="s">
+      <c r="E35" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="F35" s="12" t="s">
+      <c r="F35" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="15">
         <v>9.0</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="15">
         <v>6.0</v>
       </c>
-      <c r="I35" s="14">
+      <c r="I35" s="15">
         <v>0.0</v>
       </c>
-      <c r="J35" s="37" t="s">
+      <c r="J35" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="K35" s="1"/>
-      <c r="L35" s="38">
-        <v>95.0</v>
-      </c>
-      <c r="M35" s="17">
-        <v>93.0</v>
-      </c>
-      <c r="N35" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O35" s="17">
-        <v>92.0</v>
-      </c>
-      <c r="P35" s="17">
-        <v>94.0</v>
+      <c r="K35" s="45"/>
+      <c r="L35" s="46">
+        <v>93.33</v>
+      </c>
+      <c r="M35" s="18">
+        <v>86.66</v>
+      </c>
+      <c r="N35" s="18">
+        <v>93.33</v>
+      </c>
+      <c r="O35" s="18">
+        <v>86.66</v>
+      </c>
+      <c r="P35" s="18">
+        <v>93.33</v>
       </c>
       <c r="Q35" s="1"/>
       <c r="R35" s="1"/>
@@ -3582,48 +3709,48 @@
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C36" s="12">
+      <c r="C36" s="13">
         <v>4.0</v>
       </c>
-      <c r="D36" s="13" t="s">
+      <c r="D36" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E36" s="12" t="s">
+      <c r="E36" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="F36" s="12" t="s">
+      <c r="F36" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="15">
         <v>11.0</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="15">
         <v>5.0</v>
       </c>
-      <c r="I36" s="14">
+      <c r="I36" s="15">
         <v>0.0</v>
       </c>
-      <c r="J36" s="41" t="s">
+      <c r="J36" s="50" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="1"/>
-      <c r="L36" s="40">
-        <v>96.0</v>
-      </c>
-      <c r="M36" s="17">
-        <v>96.0</v>
-      </c>
-      <c r="N36" s="17">
-        <v>95.0</v>
-      </c>
-      <c r="O36" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="P36" s="17">
-        <v>95.0</v>
+      <c r="K36" s="51"/>
+      <c r="L36" s="49">
+        <v>93.75</v>
+      </c>
+      <c r="M36" s="18">
+        <v>93.75</v>
+      </c>
+      <c r="N36" s="18">
+        <v>93.75</v>
+      </c>
+      <c r="O36" s="18">
+        <v>87.5</v>
+      </c>
+      <c r="P36" s="18">
+        <v>93.75</v>
       </c>
       <c r="Q36" s="1"/>
       <c r="R36" s="1"/>
@@ -3633,48 +3760,48 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="11" t="s">
+      <c r="B37" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="C37" s="12">
+      <c r="C37" s="13">
         <v>5.0</v>
       </c>
-      <c r="D37" s="13" t="s">
+      <c r="D37" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="E37" s="12" t="s">
+      <c r="E37" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="F37" s="12" t="s">
+      <c r="F37" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="15">
         <v>10.0</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="15">
         <v>6.0</v>
       </c>
-      <c r="I37" s="14">
+      <c r="I37" s="15">
         <v>2.0</v>
       </c>
-      <c r="J37" s="37" t="s">
+      <c r="J37" s="44" t="s">
         <v>86</v>
       </c>
-      <c r="K37" s="1"/>
-      <c r="L37" s="38">
-        <v>92.0</v>
-      </c>
-      <c r="M37" s="17">
-        <v>72.0</v>
-      </c>
-      <c r="N37" s="17">
-        <v>94.0</v>
-      </c>
-      <c r="O37" s="17">
+      <c r="K37" s="45"/>
+      <c r="L37" s="46">
+        <v>87.5</v>
+      </c>
+      <c r="M37" s="18">
         <v>75.0</v>
       </c>
-      <c r="P37" s="17">
-        <v>92.0</v>
+      <c r="N37" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="O37" s="18">
+        <v>75.0</v>
+      </c>
+      <c r="P37" s="18">
+        <v>87.5</v>
       </c>
       <c r="Q37" s="1"/>
       <c r="R37" s="1"/>
@@ -3684,17 +3811,17 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="42"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="44"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="45"/>
-      <c r="H38" s="45"/>
-      <c r="I38" s="45"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="32"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="53"/>
+      <c r="D38" s="54"/>
+      <c r="E38" s="53"/>
+      <c r="F38" s="53"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="55"/>
+      <c r="J38" s="40"/>
+      <c r="K38" s="40"/>
+      <c r="L38" s="40"/>
       <c r="M38" s="1"/>
       <c r="N38" s="1"/>
       <c r="O38" s="1"/>
@@ -3707,17 +3834,17 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="42"/>
-      <c r="C39" s="43"/>
-      <c r="D39" s="44"/>
-      <c r="E39" s="43"/>
-      <c r="F39" s="43"/>
-      <c r="G39" s="45"/>
-      <c r="H39" s="45"/>
-      <c r="I39" s="45"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="32"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="53"/>
+      <c r="D39" s="54"/>
+      <c r="E39" s="53"/>
+      <c r="F39" s="53"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="55"/>
+      <c r="J39" s="40"/>
+      <c r="K39" s="40"/>
+      <c r="L39" s="40"/>
       <c r="M39" s="1"/>
       <c r="N39" s="1"/>
       <c r="O39" s="1"/>
@@ -3730,21 +3857,38 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="42"/>
-      <c r="C40" s="43"/>
-      <c r="D40" s="44"/>
-      <c r="E40" s="43"/>
-      <c r="F40" s="43"/>
-      <c r="G40" s="45"/>
-      <c r="H40" s="45"/>
-      <c r="I40" s="45"/>
-      <c r="J40" s="32"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="32"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="53"/>
+      <c r="D40" s="54"/>
+      <c r="E40" s="53"/>
+      <c r="F40" s="53"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="55"/>
+      <c r="J40" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="K40" s="40"/>
+      <c r="L40" s="40">
+        <f t="shared" ref="L40:P40" si="3">ROUND(AVERAGE(L8:L12),2)</f>
+        <v>95.55</v>
+      </c>
+      <c r="M40" s="40">
+        <f t="shared" si="3"/>
+        <v>94.38</v>
+      </c>
+      <c r="N40" s="40">
+        <f t="shared" si="3"/>
+        <v>93.33</v>
+      </c>
+      <c r="O40" s="40">
+        <f t="shared" si="3"/>
+        <v>94.44</v>
+      </c>
+      <c r="P40" s="40">
+        <f t="shared" si="3"/>
+        <v>94.5</v>
+      </c>
       <c r="Q40" s="1"/>
       <c r="R40" s="1"/>
       <c r="S40" s="1"/>
@@ -3753,23 +3897,40 @@
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" s="43"/>
-      <c r="D41" s="44"/>
-      <c r="E41" s="43"/>
-      <c r="F41" s="43"/>
-      <c r="G41" s="45"/>
-      <c r="H41" s="45"/>
-      <c r="I41" s="45"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="32"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
+      <c r="B41" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="53"/>
+      <c r="D41" s="54"/>
+      <c r="E41" s="53"/>
+      <c r="F41" s="53"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="55"/>
+      <c r="J41" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="K41" s="40"/>
+      <c r="L41" s="40">
+        <f t="shared" ref="L41:P41" si="4">ROUND(AVERAGE(L13:L17),2)</f>
+        <v>98.89</v>
+      </c>
+      <c r="M41" s="40">
+        <f t="shared" si="4"/>
+        <v>93.36</v>
+      </c>
+      <c r="N41" s="40">
+        <f t="shared" si="4"/>
+        <v>93.59</v>
+      </c>
+      <c r="O41" s="40">
+        <f t="shared" si="4"/>
+        <v>94.7</v>
+      </c>
+      <c r="P41" s="40">
+        <f t="shared" si="4"/>
+        <v>93.3</v>
+      </c>
       <c r="Q41" s="1"/>
       <c r="R41" s="1"/>
       <c r="S41" s="1"/>
@@ -3778,21 +3939,38 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="42"/>
-      <c r="C42" s="43"/>
-      <c r="D42" s="44"/>
-      <c r="E42" s="43"/>
-      <c r="F42" s="43"/>
-      <c r="G42" s="45"/>
-      <c r="H42" s="45"/>
-      <c r="I42" s="45"/>
-      <c r="J42" s="32"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="32"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="53"/>
+      <c r="D42" s="54"/>
+      <c r="E42" s="53"/>
+      <c r="F42" s="53"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="K42" s="40"/>
+      <c r="L42" s="40">
+        <f t="shared" ref="L42:P42" si="5">ROUND(AVERAGE(L18:L22),2)</f>
+        <v>88.75</v>
+      </c>
+      <c r="M42" s="40">
+        <f t="shared" si="5"/>
+        <v>95.49</v>
+      </c>
+      <c r="N42" s="40">
+        <f t="shared" si="5"/>
+        <v>93.38</v>
+      </c>
+      <c r="O42" s="40">
+        <f t="shared" si="5"/>
+        <v>86.65</v>
+      </c>
+      <c r="P42" s="40">
+        <f t="shared" si="5"/>
+        <v>87.83</v>
+      </c>
       <c r="Q42" s="1"/>
       <c r="R42" s="1"/>
       <c r="S42" s="1"/>
@@ -3801,21 +3979,38 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="42"/>
-      <c r="C43" s="43"/>
-      <c r="D43" s="44"/>
-      <c r="E43" s="43"/>
-      <c r="F43" s="43"/>
-      <c r="G43" s="45"/>
-      <c r="H43" s="45"/>
-      <c r="I43" s="45"/>
-      <c r="J43" s="32"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="32"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="53"/>
+      <c r="D43" s="54"/>
+      <c r="E43" s="53"/>
+      <c r="F43" s="53"/>
+      <c r="G43" s="55"/>
+      <c r="H43" s="55"/>
+      <c r="I43" s="55"/>
+      <c r="J43" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="K43" s="40"/>
+      <c r="L43" s="40">
+        <f t="shared" ref="L43:P43" si="6">ROUND(AVERAGE(L23:L27),2)</f>
+        <v>94.37</v>
+      </c>
+      <c r="M43" s="40">
+        <f t="shared" si="6"/>
+        <v>88.64</v>
+      </c>
+      <c r="N43" s="40">
+        <f t="shared" si="6"/>
+        <v>93.03</v>
+      </c>
+      <c r="O43" s="40">
+        <f t="shared" si="6"/>
+        <v>90.06</v>
+      </c>
+      <c r="P43" s="40">
+        <f t="shared" si="6"/>
+        <v>94.37</v>
+      </c>
       <c r="Q43" s="1"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
@@ -3824,16 +4019,38 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="42"/>
-      <c r="C44" s="43"/>
-      <c r="D44" s="44"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="45"/>
-      <c r="H44" s="45"/>
-      <c r="I44" s="45"/>
-      <c r="J44" s="32"/>
-      <c r="K44" s="1"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="53"/>
+      <c r="D44" s="54"/>
+      <c r="E44" s="53"/>
+      <c r="F44" s="53"/>
+      <c r="G44" s="55"/>
+      <c r="H44" s="55"/>
+      <c r="I44" s="55"/>
+      <c r="J44" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="K44" s="40"/>
+      <c r="L44" s="40">
+        <f t="shared" ref="L44:P44" si="7">ROUND(AVERAGE(L28:L32),2)</f>
+        <v>92.95</v>
+      </c>
+      <c r="M44" s="40">
+        <f t="shared" si="7"/>
+        <v>92.95</v>
+      </c>
+      <c r="N44" s="40">
+        <f t="shared" si="7"/>
+        <v>92.95</v>
+      </c>
+      <c r="O44" s="40">
+        <f t="shared" si="7"/>
+        <v>90.09</v>
+      </c>
+      <c r="P44" s="40">
+        <f t="shared" si="7"/>
+        <v>92.95</v>
+      </c>
       <c r="Q44" s="1"/>
       <c r="R44" s="1"/>
       <c r="S44" s="1"/>
@@ -3842,21 +4059,38 @@
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="42"/>
-      <c r="C45" s="43"/>
-      <c r="D45" s="44"/>
-      <c r="E45" s="43"/>
-      <c r="F45" s="43"/>
-      <c r="G45" s="45"/>
-      <c r="H45" s="45"/>
-      <c r="I45" s="45"/>
-      <c r="J45" s="32"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="32"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="53"/>
+      <c r="D45" s="54"/>
+      <c r="E45" s="53"/>
+      <c r="F45" s="53"/>
+      <c r="G45" s="55"/>
+      <c r="H45" s="55"/>
+      <c r="I45" s="55"/>
+      <c r="J45" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K45" s="40"/>
+      <c r="L45" s="40">
+        <f t="shared" ref="L45:P45" si="8">ROUND(AVERAGE(L33:L37),2)</f>
+        <v>92.24</v>
+      </c>
+      <c r="M45" s="40">
+        <f t="shared" si="8"/>
+        <v>86.97</v>
+      </c>
+      <c r="N45" s="40">
+        <f t="shared" si="8"/>
+        <v>93.42</v>
+      </c>
+      <c r="O45" s="40">
+        <f t="shared" si="8"/>
+        <v>85.72</v>
+      </c>
+      <c r="P45" s="40">
+        <f t="shared" si="8"/>
+        <v>92.24</v>
+      </c>
       <c r="Q45" s="1"/>
       <c r="R45" s="1"/>
       <c r="S45" s="1"/>
@@ -3865,17 +4099,17 @@
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="42"/>
-      <c r="C46" s="43"/>
-      <c r="D46" s="44"/>
-      <c r="E46" s="43"/>
-      <c r="F46" s="43"/>
-      <c r="G46" s="45"/>
-      <c r="H46" s="45"/>
-      <c r="I46" s="45"/>
-      <c r="J46" s="32"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="32"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="54"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="53"/>
+      <c r="G46" s="55"/>
+      <c r="H46" s="55"/>
+      <c r="I46" s="55"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="40"/>
       <c r="M46" s="1"/>
       <c r="N46" s="1"/>
       <c r="O46" s="1"/>
@@ -3888,17 +4122,17 @@
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="42"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="44"/>
-      <c r="E47" s="43"/>
-      <c r="F47" s="43"/>
-      <c r="G47" s="45"/>
-      <c r="H47" s="45"/>
-      <c r="I47" s="45"/>
-      <c r="J47" s="32"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="32"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="54"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="53"/>
+      <c r="G47" s="55"/>
+      <c r="H47" s="55"/>
+      <c r="I47" s="55"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="40"/>
       <c r="M47" s="1"/>
       <c r="N47" s="1"/>
       <c r="O47" s="1"/>
@@ -3911,17 +4145,17 @@
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="42"/>
-      <c r="C48" s="43"/>
-      <c r="D48" s="44"/>
-      <c r="E48" s="43"/>
-      <c r="F48" s="43"/>
-      <c r="G48" s="45"/>
-      <c r="H48" s="45"/>
-      <c r="I48" s="45"/>
-      <c r="J48" s="32"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="32"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="54"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="53"/>
+      <c r="G48" s="55"/>
+      <c r="H48" s="55"/>
+      <c r="I48" s="55"/>
+      <c r="J48" s="40"/>
+      <c r="K48" s="40"/>
+      <c r="L48" s="40"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
       <c r="O48" s="1"/>
@@ -3934,17 +4168,17 @@
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="42"/>
-      <c r="C49" s="43"/>
-      <c r="D49" s="44"/>
-      <c r="E49" s="43"/>
-      <c r="F49" s="43"/>
-      <c r="G49" s="45"/>
-      <c r="H49" s="45"/>
-      <c r="I49" s="45"/>
-      <c r="J49" s="32"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="32"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="54"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="53"/>
+      <c r="G49" s="55"/>
+      <c r="H49" s="55"/>
+      <c r="I49" s="55"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
+      <c r="L49" s="40"/>
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
       <c r="O49" s="1"/>
@@ -3957,17 +4191,17 @@
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="42"/>
-      <c r="C50" s="43"/>
-      <c r="D50" s="44"/>
-      <c r="E50" s="43"/>
-      <c r="F50" s="43"/>
-      <c r="G50" s="45"/>
-      <c r="H50" s="45"/>
-      <c r="I50" s="45"/>
-      <c r="J50" s="32"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="32"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="54"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="53"/>
+      <c r="G50" s="55"/>
+      <c r="H50" s="55"/>
+      <c r="I50" s="55"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
+      <c r="L50" s="40"/>
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
       <c r="O50" s="1"/>
@@ -3980,17 +4214,17 @@
     </row>
     <row r="51" ht="15.75" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="42"/>
-      <c r="C51" s="43"/>
-      <c r="D51" s="44"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="45"/>
-      <c r="H51" s="45"/>
-      <c r="I51" s="45"/>
-      <c r="J51" s="32"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="32"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="54"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="53"/>
+      <c r="G51" s="55"/>
+      <c r="H51" s="55"/>
+      <c r="I51" s="55"/>
+      <c r="J51" s="40"/>
+      <c r="K51" s="40"/>
+      <c r="L51" s="40"/>
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
       <c r="O51" s="1"/>
@@ -4003,17 +4237,17 @@
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="42"/>
-      <c r="C52" s="43"/>
-      <c r="D52" s="44"/>
-      <c r="E52" s="43"/>
-      <c r="F52" s="43"/>
-      <c r="G52" s="45"/>
-      <c r="H52" s="45"/>
-      <c r="I52" s="45"/>
-      <c r="J52" s="32"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="32"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="54"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="55"/>
+      <c r="H52" s="55"/>
+      <c r="I52" s="55"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
+      <c r="L52" s="40"/>
       <c r="M52" s="1"/>
       <c r="N52" s="1"/>
       <c r="O52" s="1"/>
@@ -4026,17 +4260,17 @@
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="42"/>
-      <c r="C53" s="43"/>
-      <c r="D53" s="44"/>
-      <c r="E53" s="43"/>
-      <c r="F53" s="43"/>
-      <c r="G53" s="45"/>
-      <c r="H53" s="45"/>
-      <c r="I53" s="45"/>
-      <c r="J53" s="32"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="32"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="54"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="53"/>
+      <c r="G53" s="55"/>
+      <c r="H53" s="55"/>
+      <c r="I53" s="55"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="40"/>
       <c r="M53" s="1"/>
       <c r="N53" s="1"/>
       <c r="O53" s="1"/>
@@ -4049,17 +4283,17 @@
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="42"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="44"/>
-      <c r="E54" s="43"/>
-      <c r="F54" s="43"/>
-      <c r="G54" s="45"/>
-      <c r="H54" s="45"/>
-      <c r="I54" s="45"/>
-      <c r="J54" s="32"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="32"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="54"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="53"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+      <c r="J54" s="40"/>
+      <c r="K54" s="40"/>
+      <c r="L54" s="40"/>
       <c r="M54" s="1"/>
       <c r="N54" s="1"/>
       <c r="O54" s="1"/>
@@ -4072,17 +4306,17 @@
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="42"/>
-      <c r="C55" s="43"/>
-      <c r="D55" s="44"/>
-      <c r="E55" s="43"/>
-      <c r="F55" s="43"/>
-      <c r="G55" s="45"/>
-      <c r="H55" s="45"/>
-      <c r="I55" s="45"/>
-      <c r="J55" s="32"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="32"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="54"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="53"/>
+      <c r="G55" s="55"/>
+      <c r="H55" s="55"/>
+      <c r="I55" s="55"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="40"/>
       <c r="M55" s="1"/>
       <c r="N55" s="1"/>
       <c r="O55" s="1"/>
@@ -4095,17 +4329,17 @@
     </row>
     <row r="56" ht="15.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="42"/>
-      <c r="C56" s="43"/>
-      <c r="D56" s="44"/>
-      <c r="E56" s="43"/>
-      <c r="F56" s="43"/>
-      <c r="G56" s="45"/>
-      <c r="H56" s="45"/>
-      <c r="I56" s="45"/>
-      <c r="J56" s="32"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="32"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="54"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="53"/>
+      <c r="G56" s="55"/>
+      <c r="H56" s="55"/>
+      <c r="I56" s="55"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="40"/>
       <c r="M56" s="1"/>
       <c r="N56" s="1"/>
       <c r="O56" s="1"/>
@@ -4118,17 +4352,17 @@
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="42"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="44"/>
-      <c r="E57" s="43"/>
-      <c r="F57" s="43"/>
-      <c r="G57" s="45"/>
-      <c r="H57" s="45"/>
-      <c r="I57" s="45"/>
-      <c r="J57" s="32"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="32"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="54"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="53"/>
+      <c r="G57" s="55"/>
+      <c r="H57" s="55"/>
+      <c r="I57" s="55"/>
+      <c r="J57" s="40"/>
+      <c r="K57" s="40"/>
+      <c r="L57" s="40"/>
       <c r="M57" s="1"/>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -4141,17 +4375,17 @@
     </row>
     <row r="58" ht="15.75" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="42"/>
-      <c r="C58" s="43"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="43"/>
-      <c r="F58" s="43"/>
-      <c r="G58" s="45"/>
-      <c r="H58" s="45"/>
-      <c r="I58" s="45"/>
-      <c r="J58" s="32"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="32"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="54"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="40"/>
       <c r="M58" s="1"/>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -4164,17 +4398,17 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="42"/>
-      <c r="C59" s="43"/>
-      <c r="D59" s="44"/>
-      <c r="E59" s="43"/>
-      <c r="F59" s="43"/>
-      <c r="G59" s="45"/>
-      <c r="H59" s="45"/>
-      <c r="I59" s="45"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="32"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="54"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="53"/>
+      <c r="G59" s="55"/>
+      <c r="H59" s="55"/>
+      <c r="I59" s="55"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="40"/>
       <c r="M59" s="1"/>
       <c r="N59" s="1"/>
       <c r="O59" s="1"/>
@@ -4187,17 +4421,17 @@
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="42"/>
-      <c r="C60" s="43"/>
-      <c r="D60" s="44"/>
-      <c r="E60" s="43"/>
-      <c r="F60" s="43"/>
-      <c r="G60" s="45"/>
-      <c r="H60" s="45"/>
-      <c r="I60" s="45"/>
-      <c r="J60" s="32"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="32"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="54"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="53"/>
+      <c r="G60" s="55"/>
+      <c r="H60" s="55"/>
+      <c r="I60" s="55"/>
+      <c r="J60" s="40"/>
+      <c r="K60" s="40"/>
+      <c r="L60" s="40"/>
       <c r="M60" s="1"/>
       <c r="N60" s="1"/>
       <c r="O60" s="1"/>
@@ -4210,17 +4444,17 @@
     </row>
     <row r="61" ht="15.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="42"/>
-      <c r="C61" s="43"/>
-      <c r="D61" s="44"/>
-      <c r="E61" s="43"/>
-      <c r="F61" s="43"/>
-      <c r="G61" s="45"/>
-      <c r="H61" s="45"/>
-      <c r="I61" s="45"/>
-      <c r="J61" s="32"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="32"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="54"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="53"/>
+      <c r="G61" s="55"/>
+      <c r="H61" s="55"/>
+      <c r="I61" s="55"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="40"/>
       <c r="M61" s="1"/>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
@@ -4233,17 +4467,17 @@
     </row>
     <row r="62" ht="15.75" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="42"/>
-      <c r="C62" s="43"/>
-      <c r="D62" s="44"/>
-      <c r="E62" s="43"/>
-      <c r="F62" s="43"/>
-      <c r="G62" s="45"/>
-      <c r="H62" s="45"/>
-      <c r="I62" s="45"/>
-      <c r="J62" s="32"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="32"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="54"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="55"/>
+      <c r="H62" s="55"/>
+      <c r="I62" s="55"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
+      <c r="L62" s="40"/>
       <c r="M62" s="1"/>
       <c r="N62" s="1"/>
       <c r="O62" s="1"/>
@@ -4256,17 +4490,17 @@
     </row>
     <row r="63" ht="15.75" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="42"/>
-      <c r="C63" s="43"/>
-      <c r="D63" s="44"/>
-      <c r="E63" s="43"/>
-      <c r="F63" s="43"/>
-      <c r="G63" s="45"/>
-      <c r="H63" s="45"/>
-      <c r="I63" s="45"/>
-      <c r="J63" s="32"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="32"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="54"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="53"/>
+      <c r="G63" s="55"/>
+      <c r="H63" s="55"/>
+      <c r="I63" s="55"/>
+      <c r="J63" s="40"/>
+      <c r="K63" s="40"/>
+      <c r="L63" s="40"/>
       <c r="M63" s="1"/>
       <c r="N63" s="1"/>
       <c r="O63" s="1"/>
@@ -4279,17 +4513,17 @@
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="42"/>
-      <c r="C64" s="43"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="43"/>
-      <c r="F64" s="43"/>
-      <c r="G64" s="45"/>
-      <c r="H64" s="45"/>
-      <c r="I64" s="45"/>
-      <c r="J64" s="32"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="32"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="54"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="55"/>
+      <c r="H64" s="55"/>
+      <c r="I64" s="55"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
+      <c r="L64" s="40"/>
       <c r="M64" s="1"/>
       <c r="N64" s="1"/>
       <c r="O64" s="1"/>
@@ -4302,17 +4536,17 @@
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="42"/>
-      <c r="C65" s="43"/>
-      <c r="D65" s="44"/>
-      <c r="E65" s="43"/>
-      <c r="F65" s="43"/>
-      <c r="G65" s="45"/>
-      <c r="H65" s="45"/>
-      <c r="I65" s="45"/>
-      <c r="J65" s="32"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="32"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="54"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="53"/>
+      <c r="G65" s="55"/>
+      <c r="H65" s="55"/>
+      <c r="I65" s="55"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
+      <c r="L65" s="40"/>
       <c r="M65" s="1"/>
       <c r="N65" s="1"/>
       <c r="O65" s="1"/>
@@ -4325,17 +4559,17 @@
     </row>
     <row r="66" ht="15.75" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="42"/>
-      <c r="C66" s="43"/>
-      <c r="D66" s="44"/>
-      <c r="E66" s="43"/>
-      <c r="F66" s="43"/>
-      <c r="G66" s="45"/>
-      <c r="H66" s="45"/>
-      <c r="I66" s="45"/>
-      <c r="J66" s="32"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="32"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="54"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="53"/>
+      <c r="G66" s="55"/>
+      <c r="H66" s="55"/>
+      <c r="I66" s="55"/>
+      <c r="J66" s="40"/>
+      <c r="K66" s="40"/>
+      <c r="L66" s="40"/>
       <c r="M66" s="1"/>
       <c r="N66" s="1"/>
       <c r="O66" s="1"/>
@@ -4348,17 +4582,17 @@
     </row>
     <row r="67" ht="15.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="42"/>
-      <c r="C67" s="43"/>
-      <c r="D67" s="44"/>
-      <c r="E67" s="43"/>
-      <c r="F67" s="43"/>
-      <c r="G67" s="45"/>
-      <c r="H67" s="45"/>
-      <c r="I67" s="45"/>
-      <c r="J67" s="32"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="32"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="54"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="53"/>
+      <c r="G67" s="55"/>
+      <c r="H67" s="55"/>
+      <c r="I67" s="55"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="40"/>
+      <c r="L67" s="40"/>
       <c r="M67" s="1"/>
       <c r="N67" s="1"/>
       <c r="O67" s="1"/>
@@ -4371,17 +4605,17 @@
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="42"/>
-      <c r="C68" s="43"/>
-      <c r="D68" s="44"/>
-      <c r="E68" s="43"/>
-      <c r="F68" s="43"/>
-      <c r="G68" s="45"/>
-      <c r="H68" s="45"/>
-      <c r="I68" s="45"/>
-      <c r="J68" s="32"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="32"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="54"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="53"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55"/>
+      <c r="J68" s="40"/>
+      <c r="K68" s="40"/>
+      <c r="L68" s="40"/>
       <c r="M68" s="1"/>
       <c r="N68" s="1"/>
       <c r="O68" s="1"/>
@@ -4394,17 +4628,17 @@
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="42"/>
-      <c r="C69" s="43"/>
-      <c r="D69" s="44"/>
-      <c r="E69" s="43"/>
-      <c r="F69" s="43"/>
-      <c r="G69" s="45"/>
-      <c r="H69" s="45"/>
-      <c r="I69" s="45"/>
-      <c r="J69" s="32"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="32"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="54"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="53"/>
+      <c r="G69" s="55"/>
+      <c r="H69" s="55"/>
+      <c r="I69" s="55"/>
+      <c r="J69" s="40"/>
+      <c r="K69" s="40"/>
+      <c r="L69" s="40"/>
       <c r="M69" s="1"/>
       <c r="N69" s="1"/>
       <c r="O69" s="1"/>
@@ -4417,17 +4651,17 @@
     </row>
     <row r="70" ht="15.75" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="42"/>
-      <c r="C70" s="43"/>
-      <c r="D70" s="44"/>
-      <c r="E70" s="43"/>
-      <c r="F70" s="43"/>
-      <c r="G70" s="45"/>
-      <c r="H70" s="45"/>
-      <c r="I70" s="45"/>
-      <c r="J70" s="32"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="32"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="54"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="53"/>
+      <c r="G70" s="55"/>
+      <c r="H70" s="55"/>
+      <c r="I70" s="55"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
+      <c r="L70" s="40"/>
       <c r="M70" s="1"/>
       <c r="N70" s="1"/>
       <c r="O70" s="1"/>
@@ -4440,17 +4674,17 @@
     </row>
     <row r="71" ht="15.75" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="42"/>
-      <c r="C71" s="43"/>
-      <c r="D71" s="44"/>
-      <c r="E71" s="43"/>
-      <c r="F71" s="43"/>
-      <c r="G71" s="45"/>
-      <c r="H71" s="45"/>
-      <c r="I71" s="45"/>
-      <c r="J71" s="32"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="32"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="53"/>
+      <c r="D71" s="54"/>
+      <c r="E71" s="53"/>
+      <c r="F71" s="53"/>
+      <c r="G71" s="55"/>
+      <c r="H71" s="55"/>
+      <c r="I71" s="55"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="40"/>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
       <c r="O71" s="1"/>
@@ -4463,17 +4697,17 @@
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="42"/>
-      <c r="C72" s="43"/>
-      <c r="D72" s="44"/>
-      <c r="E72" s="43"/>
-      <c r="F72" s="43"/>
-      <c r="G72" s="45"/>
-      <c r="H72" s="45"/>
-      <c r="I72" s="45"/>
-      <c r="J72" s="32"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="32"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="54"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="53"/>
+      <c r="G72" s="55"/>
+      <c r="H72" s="55"/>
+      <c r="I72" s="55"/>
+      <c r="J72" s="40"/>
+      <c r="K72" s="40"/>
+      <c r="L72" s="40"/>
       <c r="M72" s="1"/>
       <c r="N72" s="1"/>
       <c r="O72" s="1"/>
@@ -4486,17 +4720,17 @@
     </row>
     <row r="73" ht="15.75" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="42"/>
-      <c r="C73" s="43"/>
-      <c r="D73" s="44"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="45"/>
-      <c r="H73" s="45"/>
-      <c r="I73" s="45"/>
-      <c r="J73" s="32"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="32"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="54"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="53"/>
+      <c r="G73" s="55"/>
+      <c r="H73" s="55"/>
+      <c r="I73" s="55"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="40"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
       <c r="O73" s="1"/>
@@ -4509,17 +4743,17 @@
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="42"/>
-      <c r="C74" s="43"/>
-      <c r="D74" s="44"/>
-      <c r="E74" s="43"/>
-      <c r="F74" s="43"/>
-      <c r="G74" s="45"/>
-      <c r="H74" s="45"/>
-      <c r="I74" s="45"/>
-      <c r="J74" s="32"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="32"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="54"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="53"/>
+      <c r="G74" s="55"/>
+      <c r="H74" s="55"/>
+      <c r="I74" s="55"/>
+      <c r="J74" s="40"/>
+      <c r="K74" s="40"/>
+      <c r="L74" s="40"/>
       <c r="M74" s="1"/>
       <c r="N74" s="1"/>
       <c r="O74" s="1"/>
@@ -4532,17 +4766,17 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="42"/>
-      <c r="C75" s="43"/>
-      <c r="D75" s="44"/>
-      <c r="E75" s="43"/>
-      <c r="F75" s="43"/>
-      <c r="G75" s="45"/>
-      <c r="H75" s="45"/>
-      <c r="I75" s="45"/>
-      <c r="J75" s="32"/>
-      <c r="K75" s="1"/>
-      <c r="L75" s="32"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="54"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="53"/>
+      <c r="G75" s="55"/>
+      <c r="H75" s="55"/>
+      <c r="I75" s="55"/>
+      <c r="J75" s="40"/>
+      <c r="K75" s="40"/>
+      <c r="L75" s="40"/>
       <c r="M75" s="1"/>
       <c r="N75" s="1"/>
       <c r="O75" s="1"/>
@@ -4555,17 +4789,17 @@
     </row>
     <row r="76" ht="15.75" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="42"/>
-      <c r="C76" s="43"/>
-      <c r="D76" s="44"/>
-      <c r="E76" s="43"/>
-      <c r="F76" s="43"/>
-      <c r="G76" s="45"/>
-      <c r="H76" s="45"/>
-      <c r="I76" s="45"/>
-      <c r="J76" s="32"/>
-      <c r="K76" s="1"/>
-      <c r="L76" s="32"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="54"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="53"/>
+      <c r="G76" s="55"/>
+      <c r="H76" s="55"/>
+      <c r="I76" s="55"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
+      <c r="L76" s="40"/>
       <c r="M76" s="1"/>
       <c r="N76" s="1"/>
       <c r="O76" s="1"/>
@@ -4578,17 +4812,17 @@
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="42"/>
-      <c r="C77" s="43"/>
-      <c r="D77" s="44"/>
-      <c r="E77" s="43"/>
-      <c r="F77" s="43"/>
-      <c r="G77" s="45"/>
-      <c r="H77" s="45"/>
-      <c r="I77" s="45"/>
-      <c r="J77" s="32"/>
-      <c r="K77" s="1"/>
-      <c r="L77" s="32"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="54"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="53"/>
+      <c r="G77" s="55"/>
+      <c r="H77" s="55"/>
+      <c r="I77" s="55"/>
+      <c r="J77" s="40"/>
+      <c r="K77" s="40"/>
+      <c r="L77" s="40"/>
       <c r="M77" s="1"/>
       <c r="N77" s="1"/>
       <c r="O77" s="1"/>
@@ -4601,17 +4835,17 @@
     </row>
     <row r="78" ht="15.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="42"/>
-      <c r="C78" s="43"/>
-      <c r="D78" s="44"/>
-      <c r="E78" s="43"/>
-      <c r="F78" s="43"/>
-      <c r="G78" s="45"/>
-      <c r="H78" s="45"/>
-      <c r="I78" s="45"/>
-      <c r="J78" s="32"/>
-      <c r="K78" s="1"/>
-      <c r="L78" s="32"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="54"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="53"/>
+      <c r="G78" s="55"/>
+      <c r="H78" s="55"/>
+      <c r="I78" s="55"/>
+      <c r="J78" s="40"/>
+      <c r="K78" s="40"/>
+      <c r="L78" s="40"/>
       <c r="M78" s="1"/>
       <c r="N78" s="1"/>
       <c r="O78" s="1"/>
@@ -4624,17 +4858,17 @@
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="42"/>
-      <c r="C79" s="43"/>
-      <c r="D79" s="44"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="45"/>
-      <c r="H79" s="45"/>
-      <c r="I79" s="45"/>
-      <c r="J79" s="32"/>
-      <c r="K79" s="1"/>
-      <c r="L79" s="32"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="54"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="53"/>
+      <c r="G79" s="55"/>
+      <c r="H79" s="55"/>
+      <c r="I79" s="55"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="40"/>
+      <c r="L79" s="40"/>
       <c r="M79" s="1"/>
       <c r="N79" s="1"/>
       <c r="O79" s="1"/>
@@ -4647,17 +4881,17 @@
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="42"/>
-      <c r="C80" s="43"/>
-      <c r="D80" s="44"/>
-      <c r="E80" s="43"/>
-      <c r="F80" s="43"/>
-      <c r="G80" s="45"/>
-      <c r="H80" s="45"/>
-      <c r="I80" s="45"/>
-      <c r="J80" s="32"/>
-      <c r="K80" s="1"/>
-      <c r="L80" s="32"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="54"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="53"/>
+      <c r="G80" s="55"/>
+      <c r="H80" s="55"/>
+      <c r="I80" s="55"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="40"/>
+      <c r="L80" s="40"/>
       <c r="M80" s="1"/>
       <c r="N80" s="1"/>
       <c r="O80" s="1"/>
@@ -4670,17 +4904,17 @@
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="42"/>
-      <c r="C81" s="43"/>
-      <c r="D81" s="44"/>
-      <c r="E81" s="43"/>
-      <c r="F81" s="43"/>
-      <c r="G81" s="45"/>
-      <c r="H81" s="45"/>
-      <c r="I81" s="45"/>
-      <c r="J81" s="32"/>
-      <c r="K81" s="1"/>
-      <c r="L81" s="32"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="53"/>
+      <c r="D81" s="54"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="55"/>
+      <c r="H81" s="55"/>
+      <c r="I81" s="55"/>
+      <c r="J81" s="40"/>
+      <c r="K81" s="40"/>
+      <c r="L81" s="40"/>
       <c r="M81" s="1"/>
       <c r="N81" s="1"/>
       <c r="O81" s="1"/>
@@ -4693,17 +4927,17 @@
     </row>
     <row r="82" ht="15.75" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="42"/>
-      <c r="C82" s="43"/>
-      <c r="D82" s="44"/>
-      <c r="E82" s="43"/>
-      <c r="F82" s="43"/>
-      <c r="G82" s="45"/>
-      <c r="H82" s="45"/>
-      <c r="I82" s="45"/>
-      <c r="J82" s="32"/>
-      <c r="K82" s="1"/>
-      <c r="L82" s="32"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="54"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="53"/>
+      <c r="G82" s="55"/>
+      <c r="H82" s="55"/>
+      <c r="I82" s="55"/>
+      <c r="J82" s="40"/>
+      <c r="K82" s="40"/>
+      <c r="L82" s="40"/>
       <c r="M82" s="1"/>
       <c r="N82" s="1"/>
       <c r="O82" s="1"/>
@@ -4716,17 +4950,17 @@
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="42"/>
-      <c r="C83" s="43"/>
-      <c r="D83" s="44"/>
-      <c r="E83" s="43"/>
-      <c r="F83" s="43"/>
-      <c r="G83" s="45"/>
-      <c r="H83" s="45"/>
-      <c r="I83" s="45"/>
-      <c r="J83" s="32"/>
-      <c r="K83" s="1"/>
-      <c r="L83" s="32"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="54"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="53"/>
+      <c r="G83" s="55"/>
+      <c r="H83" s="55"/>
+      <c r="I83" s="55"/>
+      <c r="J83" s="40"/>
+      <c r="K83" s="40"/>
+      <c r="L83" s="40"/>
       <c r="M83" s="1"/>
       <c r="N83" s="1"/>
       <c r="O83" s="1"/>
@@ -4739,17 +4973,17 @@
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="42"/>
-      <c r="C84" s="43"/>
-      <c r="D84" s="44"/>
-      <c r="E84" s="43"/>
-      <c r="F84" s="43"/>
-      <c r="G84" s="45"/>
-      <c r="H84" s="45"/>
-      <c r="I84" s="45"/>
-      <c r="J84" s="32"/>
-      <c r="K84" s="1"/>
-      <c r="L84" s="32"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="54"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="53"/>
+      <c r="G84" s="55"/>
+      <c r="H84" s="55"/>
+      <c r="I84" s="55"/>
+      <c r="J84" s="40"/>
+      <c r="K84" s="40"/>
+      <c r="L84" s="40"/>
       <c r="M84" s="1"/>
       <c r="N84" s="1"/>
       <c r="O84" s="1"/>
@@ -4762,17 +4996,17 @@
     </row>
     <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="42"/>
-      <c r="C85" s="43"/>
-      <c r="D85" s="44"/>
-      <c r="E85" s="43"/>
-      <c r="F85" s="43"/>
-      <c r="G85" s="45"/>
-      <c r="H85" s="45"/>
-      <c r="I85" s="45"/>
-      <c r="J85" s="32"/>
-      <c r="K85" s="1"/>
-      <c r="L85" s="32"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="54"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="55"/>
+      <c r="H85" s="55"/>
+      <c r="I85" s="55"/>
+      <c r="J85" s="40"/>
+      <c r="K85" s="40"/>
+      <c r="L85" s="40"/>
       <c r="M85" s="1"/>
       <c r="N85" s="1"/>
       <c r="O85" s="1"/>
@@ -4785,17 +5019,17 @@
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="42"/>
-      <c r="C86" s="43"/>
-      <c r="D86" s="44"/>
-      <c r="E86" s="43"/>
-      <c r="F86" s="43"/>
-      <c r="G86" s="45"/>
-      <c r="H86" s="45"/>
-      <c r="I86" s="45"/>
-      <c r="J86" s="32"/>
-      <c r="K86" s="1"/>
-      <c r="L86" s="32"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="54"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="53"/>
+      <c r="G86" s="55"/>
+      <c r="H86" s="55"/>
+      <c r="I86" s="55"/>
+      <c r="J86" s="40"/>
+      <c r="K86" s="40"/>
+      <c r="L86" s="40"/>
       <c r="M86" s="1"/>
       <c r="N86" s="1"/>
       <c r="O86" s="1"/>
@@ -4808,17 +5042,17 @@
     </row>
     <row r="87" ht="15.75" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="42"/>
-      <c r="C87" s="43"/>
-      <c r="D87" s="44"/>
-      <c r="E87" s="43"/>
-      <c r="F87" s="43"/>
-      <c r="G87" s="45"/>
-      <c r="H87" s="45"/>
-      <c r="I87" s="45"/>
-      <c r="J87" s="32"/>
-      <c r="K87" s="1"/>
-      <c r="L87" s="32"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="54"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="53"/>
+      <c r="G87" s="55"/>
+      <c r="H87" s="55"/>
+      <c r="I87" s="55"/>
+      <c r="J87" s="40"/>
+      <c r="K87" s="40"/>
+      <c r="L87" s="40"/>
       <c r="M87" s="1"/>
       <c r="N87" s="1"/>
       <c r="O87" s="1"/>
@@ -4831,17 +5065,17 @@
     </row>
     <row r="88" ht="15.75" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="42"/>
-      <c r="C88" s="43"/>
-      <c r="D88" s="44"/>
-      <c r="E88" s="43"/>
-      <c r="F88" s="43"/>
-      <c r="G88" s="45"/>
-      <c r="H88" s="45"/>
-      <c r="I88" s="45"/>
-      <c r="J88" s="32"/>
-      <c r="K88" s="1"/>
-      <c r="L88" s="32"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="54"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="53"/>
+      <c r="G88" s="55"/>
+      <c r="H88" s="55"/>
+      <c r="I88" s="55"/>
+      <c r="J88" s="40"/>
+      <c r="K88" s="40"/>
+      <c r="L88" s="40"/>
       <c r="M88" s="1"/>
       <c r="N88" s="1"/>
       <c r="O88" s="1"/>
@@ -4854,17 +5088,17 @@
     </row>
     <row r="89" ht="15.75" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="42"/>
-      <c r="C89" s="43"/>
-      <c r="D89" s="44"/>
-      <c r="E89" s="43"/>
-      <c r="F89" s="43"/>
-      <c r="G89" s="45"/>
-      <c r="H89" s="45"/>
-      <c r="I89" s="45"/>
-      <c r="J89" s="32"/>
-      <c r="K89" s="1"/>
-      <c r="L89" s="32"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="54"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="55"/>
+      <c r="H89" s="55"/>
+      <c r="I89" s="55"/>
+      <c r="J89" s="40"/>
+      <c r="K89" s="40"/>
+      <c r="L89" s="40"/>
       <c r="M89" s="1"/>
       <c r="N89" s="1"/>
       <c r="O89" s="1"/>
@@ -4877,17 +5111,17 @@
     </row>
     <row r="90" ht="15.75" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="42"/>
-      <c r="C90" s="43"/>
-      <c r="D90" s="44"/>
-      <c r="E90" s="43"/>
-      <c r="F90" s="43"/>
-      <c r="G90" s="45"/>
-      <c r="H90" s="45"/>
-      <c r="I90" s="45"/>
-      <c r="J90" s="32"/>
-      <c r="K90" s="1"/>
-      <c r="L90" s="32"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="54"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="53"/>
+      <c r="G90" s="55"/>
+      <c r="H90" s="55"/>
+      <c r="I90" s="55"/>
+      <c r="J90" s="40"/>
+      <c r="K90" s="40"/>
+      <c r="L90" s="40"/>
       <c r="M90" s="1"/>
       <c r="N90" s="1"/>
       <c r="O90" s="1"/>
@@ -4900,17 +5134,17 @@
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="42"/>
-      <c r="C91" s="43"/>
-      <c r="D91" s="44"/>
-      <c r="E91" s="43"/>
-      <c r="F91" s="43"/>
-      <c r="G91" s="45"/>
-      <c r="H91" s="45"/>
-      <c r="I91" s="45"/>
-      <c r="J91" s="32"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="32"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="53"/>
+      <c r="D91" s="54"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="53"/>
+      <c r="G91" s="55"/>
+      <c r="H91" s="55"/>
+      <c r="I91" s="55"/>
+      <c r="J91" s="40"/>
+      <c r="K91" s="40"/>
+      <c r="L91" s="40"/>
       <c r="M91" s="1"/>
       <c r="N91" s="1"/>
       <c r="O91" s="1"/>
@@ -4923,17 +5157,17 @@
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="42"/>
-      <c r="C92" s="43"/>
-      <c r="D92" s="44"/>
-      <c r="E92" s="43"/>
-      <c r="F92" s="43"/>
-      <c r="G92" s="45"/>
-      <c r="H92" s="45"/>
-      <c r="I92" s="45"/>
-      <c r="J92" s="32"/>
-      <c r="K92" s="1"/>
-      <c r="L92" s="32"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="54"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="53"/>
+      <c r="G92" s="55"/>
+      <c r="H92" s="55"/>
+      <c r="I92" s="55"/>
+      <c r="J92" s="40"/>
+      <c r="K92" s="40"/>
+      <c r="L92" s="40"/>
       <c r="M92" s="1"/>
       <c r="N92" s="1"/>
       <c r="O92" s="1"/>
@@ -4946,17 +5180,17 @@
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="42"/>
-      <c r="C93" s="43"/>
-      <c r="D93" s="44"/>
-      <c r="E93" s="43"/>
-      <c r="F93" s="43"/>
-      <c r="G93" s="45"/>
-      <c r="H93" s="45"/>
-      <c r="I93" s="45"/>
-      <c r="J93" s="32"/>
-      <c r="K93" s="1"/>
-      <c r="L93" s="32"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="54"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="53"/>
+      <c r="G93" s="55"/>
+      <c r="H93" s="55"/>
+      <c r="I93" s="55"/>
+      <c r="J93" s="40"/>
+      <c r="K93" s="40"/>
+      <c r="L93" s="40"/>
       <c r="M93" s="1"/>
       <c r="N93" s="1"/>
       <c r="O93" s="1"/>
@@ -4969,17 +5203,17 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="42"/>
-      <c r="C94" s="43"/>
-      <c r="D94" s="44"/>
-      <c r="E94" s="43"/>
-      <c r="F94" s="43"/>
-      <c r="G94" s="45"/>
-      <c r="H94" s="45"/>
-      <c r="I94" s="45"/>
-      <c r="J94" s="32"/>
-      <c r="K94" s="1"/>
-      <c r="L94" s="32"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="54"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="53"/>
+      <c r="G94" s="55"/>
+      <c r="H94" s="55"/>
+      <c r="I94" s="55"/>
+      <c r="J94" s="40"/>
+      <c r="K94" s="40"/>
+      <c r="L94" s="40"/>
       <c r="M94" s="1"/>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
@@ -4992,17 +5226,17 @@
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="42"/>
-      <c r="C95" s="43"/>
-      <c r="D95" s="44"/>
-      <c r="E95" s="43"/>
-      <c r="F95" s="43"/>
-      <c r="G95" s="45"/>
-      <c r="H95" s="45"/>
-      <c r="I95" s="45"/>
-      <c r="J95" s="32"/>
-      <c r="K95" s="1"/>
-      <c r="L95" s="32"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="53"/>
+      <c r="D95" s="54"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="53"/>
+      <c r="G95" s="55"/>
+      <c r="H95" s="55"/>
+      <c r="I95" s="55"/>
+      <c r="J95" s="40"/>
+      <c r="K95" s="40"/>
+      <c r="L95" s="40"/>
       <c r="M95" s="1"/>
       <c r="N95" s="1"/>
       <c r="O95" s="1"/>
@@ -5015,17 +5249,17 @@
     </row>
     <row r="96" ht="15.75" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="42"/>
-      <c r="C96" s="43"/>
-      <c r="D96" s="44"/>
-      <c r="E96" s="43"/>
-      <c r="F96" s="43"/>
-      <c r="G96" s="45"/>
-      <c r="H96" s="45"/>
-      <c r="I96" s="45"/>
-      <c r="J96" s="32"/>
-      <c r="K96" s="1"/>
-      <c r="L96" s="32"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="54"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="53"/>
+      <c r="G96" s="55"/>
+      <c r="H96" s="55"/>
+      <c r="I96" s="55"/>
+      <c r="J96" s="40"/>
+      <c r="K96" s="40"/>
+      <c r="L96" s="40"/>
       <c r="M96" s="1"/>
       <c r="N96" s="1"/>
       <c r="O96" s="1"/>
@@ -5038,17 +5272,17 @@
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="42"/>
-      <c r="C97" s="43"/>
-      <c r="D97" s="44"/>
-      <c r="E97" s="43"/>
-      <c r="F97" s="43"/>
-      <c r="G97" s="45"/>
-      <c r="H97" s="45"/>
-      <c r="I97" s="45"/>
-      <c r="J97" s="32"/>
-      <c r="K97" s="1"/>
-      <c r="L97" s="32"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="53"/>
+      <c r="D97" s="54"/>
+      <c r="E97" s="53"/>
+      <c r="F97" s="53"/>
+      <c r="G97" s="55"/>
+      <c r="H97" s="55"/>
+      <c r="I97" s="55"/>
+      <c r="J97" s="40"/>
+      <c r="K97" s="40"/>
+      <c r="L97" s="40"/>
       <c r="M97" s="1"/>
       <c r="N97" s="1"/>
       <c r="O97" s="1"/>
@@ -5061,17 +5295,17 @@
     </row>
     <row r="98" ht="15.75" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="42"/>
-      <c r="C98" s="43"/>
-      <c r="D98" s="44"/>
-      <c r="E98" s="43"/>
-      <c r="F98" s="43"/>
-      <c r="G98" s="45"/>
-      <c r="H98" s="45"/>
-      <c r="I98" s="45"/>
-      <c r="J98" s="32"/>
-      <c r="K98" s="1"/>
-      <c r="L98" s="32"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="54"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="53"/>
+      <c r="G98" s="55"/>
+      <c r="H98" s="55"/>
+      <c r="I98" s="55"/>
+      <c r="J98" s="40"/>
+      <c r="K98" s="40"/>
+      <c r="L98" s="40"/>
       <c r="M98" s="1"/>
       <c r="N98" s="1"/>
       <c r="O98" s="1"/>
@@ -5084,17 +5318,17 @@
     </row>
     <row r="99" ht="15.75" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="42"/>
-      <c r="C99" s="43"/>
-      <c r="D99" s="44"/>
-      <c r="E99" s="43"/>
-      <c r="F99" s="43"/>
-      <c r="G99" s="45"/>
-      <c r="H99" s="45"/>
-      <c r="I99" s="45"/>
-      <c r="J99" s="32"/>
-      <c r="K99" s="1"/>
-      <c r="L99" s="32"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="54"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="53"/>
+      <c r="G99" s="55"/>
+      <c r="H99" s="55"/>
+      <c r="I99" s="55"/>
+      <c r="J99" s="40"/>
+      <c r="K99" s="40"/>
+      <c r="L99" s="40"/>
       <c r="M99" s="1"/>
       <c r="N99" s="1"/>
       <c r="O99" s="1"/>
@@ -5107,17 +5341,17 @@
     </row>
     <row r="100" ht="15.75" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="42"/>
-      <c r="C100" s="43"/>
-      <c r="D100" s="44"/>
-      <c r="E100" s="43"/>
-      <c r="F100" s="43"/>
-      <c r="G100" s="45"/>
-      <c r="H100" s="45"/>
-      <c r="I100" s="45"/>
-      <c r="J100" s="32"/>
-      <c r="K100" s="1"/>
-      <c r="L100" s="32"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="53"/>
+      <c r="D100" s="54"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="53"/>
+      <c r="G100" s="55"/>
+      <c r="H100" s="55"/>
+      <c r="I100" s="55"/>
+      <c r="J100" s="40"/>
+      <c r="K100" s="40"/>
+      <c r="L100" s="40"/>
       <c r="M100" s="1"/>
       <c r="N100" s="1"/>
       <c r="O100" s="1"/>
@@ -5130,17 +5364,17 @@
     </row>
     <row r="101" ht="15.75" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="42"/>
-      <c r="C101" s="43"/>
-      <c r="D101" s="44"/>
-      <c r="E101" s="43"/>
-      <c r="F101" s="43"/>
-      <c r="G101" s="45"/>
-      <c r="H101" s="45"/>
-      <c r="I101" s="45"/>
-      <c r="J101" s="32"/>
-      <c r="K101" s="1"/>
-      <c r="L101" s="32"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="53"/>
+      <c r="D101" s="54"/>
+      <c r="E101" s="53"/>
+      <c r="F101" s="53"/>
+      <c r="G101" s="55"/>
+      <c r="H101" s="55"/>
+      <c r="I101" s="55"/>
+      <c r="J101" s="40"/>
+      <c r="K101" s="40"/>
+      <c r="L101" s="40"/>
       <c r="M101" s="1"/>
       <c r="N101" s="1"/>
       <c r="O101" s="1"/>
@@ -5153,17 +5387,17 @@
     </row>
     <row r="102" ht="15.75" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="42"/>
-      <c r="C102" s="43"/>
-      <c r="D102" s="44"/>
-      <c r="E102" s="43"/>
-      <c r="F102" s="43"/>
-      <c r="G102" s="45"/>
-      <c r="H102" s="45"/>
-      <c r="I102" s="45"/>
-      <c r="J102" s="32"/>
-      <c r="K102" s="1"/>
-      <c r="L102" s="32"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="54"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="53"/>
+      <c r="G102" s="55"/>
+      <c r="H102" s="55"/>
+      <c r="I102" s="55"/>
+      <c r="J102" s="40"/>
+      <c r="K102" s="40"/>
+      <c r="L102" s="40"/>
       <c r="M102" s="1"/>
       <c r="N102" s="1"/>
       <c r="O102" s="1"/>
@@ -5176,17 +5410,17 @@
     </row>
     <row r="103" ht="15.75" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="42"/>
-      <c r="C103" s="43"/>
-      <c r="D103" s="44"/>
-      <c r="E103" s="43"/>
-      <c r="F103" s="43"/>
-      <c r="G103" s="45"/>
-      <c r="H103" s="45"/>
-      <c r="I103" s="45"/>
-      <c r="J103" s="32"/>
-      <c r="K103" s="1"/>
-      <c r="L103" s="32"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="53"/>
+      <c r="D103" s="54"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="53"/>
+      <c r="G103" s="55"/>
+      <c r="H103" s="55"/>
+      <c r="I103" s="55"/>
+      <c r="J103" s="40"/>
+      <c r="K103" s="40"/>
+      <c r="L103" s="40"/>
       <c r="M103" s="1"/>
       <c r="N103" s="1"/>
       <c r="O103" s="1"/>
@@ -5199,17 +5433,17 @@
     </row>
     <row r="104" ht="15.75" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="42"/>
-      <c r="C104" s="43"/>
-      <c r="D104" s="44"/>
-      <c r="E104" s="43"/>
-      <c r="F104" s="43"/>
-      <c r="G104" s="45"/>
-      <c r="H104" s="45"/>
-      <c r="I104" s="45"/>
-      <c r="J104" s="32"/>
-      <c r="K104" s="1"/>
-      <c r="L104" s="32"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="54"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="53"/>
+      <c r="G104" s="55"/>
+      <c r="H104" s="55"/>
+      <c r="I104" s="55"/>
+      <c r="J104" s="40"/>
+      <c r="K104" s="40"/>
+      <c r="L104" s="40"/>
       <c r="M104" s="1"/>
       <c r="N104" s="1"/>
       <c r="O104" s="1"/>
@@ -5222,17 +5456,17 @@
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="42"/>
-      <c r="C105" s="43"/>
-      <c r="D105" s="44"/>
-      <c r="E105" s="43"/>
-      <c r="F105" s="43"/>
-      <c r="G105" s="45"/>
-      <c r="H105" s="45"/>
-      <c r="I105" s="45"/>
-      <c r="J105" s="32"/>
-      <c r="K105" s="1"/>
-      <c r="L105" s="32"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="54"/>
+      <c r="E105" s="53"/>
+      <c r="F105" s="53"/>
+      <c r="G105" s="55"/>
+      <c r="H105" s="55"/>
+      <c r="I105" s="55"/>
+      <c r="J105" s="40"/>
+      <c r="K105" s="40"/>
+      <c r="L105" s="40"/>
       <c r="M105" s="1"/>
       <c r="N105" s="1"/>
       <c r="O105" s="1"/>
@@ -5245,17 +5479,17 @@
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="42"/>
-      <c r="C106" s="43"/>
-      <c r="D106" s="44"/>
-      <c r="E106" s="43"/>
-      <c r="F106" s="43"/>
-      <c r="G106" s="45"/>
-      <c r="H106" s="45"/>
-      <c r="I106" s="45"/>
-      <c r="J106" s="32"/>
-      <c r="K106" s="1"/>
-      <c r="L106" s="32"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="54"/>
+      <c r="E106" s="53"/>
+      <c r="F106" s="53"/>
+      <c r="G106" s="55"/>
+      <c r="H106" s="55"/>
+      <c r="I106" s="55"/>
+      <c r="J106" s="40"/>
+      <c r="K106" s="40"/>
+      <c r="L106" s="40"/>
       <c r="M106" s="1"/>
       <c r="N106" s="1"/>
       <c r="O106" s="1"/>
@@ -5268,17 +5502,17 @@
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="42"/>
-      <c r="C107" s="43"/>
-      <c r="D107" s="44"/>
-      <c r="E107" s="43"/>
-      <c r="F107" s="43"/>
-      <c r="G107" s="45"/>
-      <c r="H107" s="45"/>
-      <c r="I107" s="45"/>
-      <c r="J107" s="32"/>
-      <c r="K107" s="1"/>
-      <c r="L107" s="32"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="53"/>
+      <c r="D107" s="54"/>
+      <c r="E107" s="53"/>
+      <c r="F107" s="53"/>
+      <c r="G107" s="55"/>
+      <c r="H107" s="55"/>
+      <c r="I107" s="55"/>
+      <c r="J107" s="40"/>
+      <c r="K107" s="40"/>
+      <c r="L107" s="40"/>
       <c r="M107" s="1"/>
       <c r="N107" s="1"/>
       <c r="O107" s="1"/>
@@ -5291,17 +5525,17 @@
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="42"/>
-      <c r="C108" s="43"/>
-      <c r="D108" s="44"/>
-      <c r="E108" s="43"/>
-      <c r="F108" s="43"/>
-      <c r="G108" s="45"/>
-      <c r="H108" s="45"/>
-      <c r="I108" s="45"/>
-      <c r="J108" s="32"/>
-      <c r="K108" s="1"/>
-      <c r="L108" s="32"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="53"/>
+      <c r="D108" s="54"/>
+      <c r="E108" s="53"/>
+      <c r="F108" s="53"/>
+      <c r="G108" s="55"/>
+      <c r="H108" s="55"/>
+      <c r="I108" s="55"/>
+      <c r="J108" s="40"/>
+      <c r="K108" s="40"/>
+      <c r="L108" s="40"/>
       <c r="M108" s="1"/>
       <c r="N108" s="1"/>
       <c r="O108" s="1"/>
@@ -5314,17 +5548,17 @@
     </row>
     <row r="109" ht="15.75" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="42"/>
-      <c r="C109" s="43"/>
-      <c r="D109" s="44"/>
-      <c r="E109" s="43"/>
-      <c r="F109" s="43"/>
-      <c r="G109" s="45"/>
-      <c r="H109" s="45"/>
-      <c r="I109" s="45"/>
-      <c r="J109" s="32"/>
-      <c r="K109" s="1"/>
-      <c r="L109" s="32"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="54"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="53"/>
+      <c r="G109" s="55"/>
+      <c r="H109" s="55"/>
+      <c r="I109" s="55"/>
+      <c r="J109" s="40"/>
+      <c r="K109" s="40"/>
+      <c r="L109" s="40"/>
       <c r="M109" s="1"/>
       <c r="N109" s="1"/>
       <c r="O109" s="1"/>
@@ -5337,17 +5571,17 @@
     </row>
     <row r="110" ht="15.75" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="42"/>
-      <c r="C110" s="43"/>
-      <c r="D110" s="44"/>
-      <c r="E110" s="43"/>
-      <c r="F110" s="43"/>
-      <c r="G110" s="45"/>
-      <c r="H110" s="45"/>
-      <c r="I110" s="45"/>
-      <c r="J110" s="32"/>
-      <c r="K110" s="1"/>
-      <c r="L110" s="32"/>
+      <c r="B110" s="52"/>
+      <c r="C110" s="53"/>
+      <c r="D110" s="54"/>
+      <c r="E110" s="53"/>
+      <c r="F110" s="53"/>
+      <c r="G110" s="55"/>
+      <c r="H110" s="55"/>
+      <c r="I110" s="55"/>
+      <c r="J110" s="40"/>
+      <c r="K110" s="40"/>
+      <c r="L110" s="40"/>
       <c r="M110" s="1"/>
       <c r="N110" s="1"/>
       <c r="O110" s="1"/>
@@ -5360,17 +5594,17 @@
     </row>
     <row r="111" ht="15.75" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="42"/>
-      <c r="C111" s="43"/>
-      <c r="D111" s="44"/>
-      <c r="E111" s="43"/>
-      <c r="F111" s="43"/>
-      <c r="G111" s="45"/>
-      <c r="H111" s="45"/>
-      <c r="I111" s="45"/>
-      <c r="J111" s="32"/>
-      <c r="K111" s="1"/>
-      <c r="L111" s="32"/>
+      <c r="B111" s="52"/>
+      <c r="C111" s="53"/>
+      <c r="D111" s="54"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="53"/>
+      <c r="G111" s="55"/>
+      <c r="H111" s="55"/>
+      <c r="I111" s="55"/>
+      <c r="J111" s="40"/>
+      <c r="K111" s="40"/>
+      <c r="L111" s="40"/>
       <c r="M111" s="1"/>
       <c r="N111" s="1"/>
       <c r="O111" s="1"/>
@@ -5383,17 +5617,17 @@
     </row>
     <row r="112" ht="15.75" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="42"/>
-      <c r="C112" s="43"/>
-      <c r="D112" s="44"/>
-      <c r="E112" s="43"/>
-      <c r="F112" s="43"/>
-      <c r="G112" s="45"/>
-      <c r="H112" s="45"/>
-      <c r="I112" s="45"/>
-      <c r="J112" s="32"/>
-      <c r="K112" s="1"/>
-      <c r="L112" s="32"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="53"/>
+      <c r="D112" s="54"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="53"/>
+      <c r="G112" s="55"/>
+      <c r="H112" s="55"/>
+      <c r="I112" s="55"/>
+      <c r="J112" s="40"/>
+      <c r="K112" s="40"/>
+      <c r="L112" s="40"/>
       <c r="M112" s="1"/>
       <c r="N112" s="1"/>
       <c r="O112" s="1"/>
@@ -5406,17 +5640,17 @@
     </row>
     <row r="113" ht="15.75" customHeight="1">
       <c r="A113" s="1"/>
-      <c r="B113" s="42"/>
-      <c r="C113" s="43"/>
-      <c r="D113" s="44"/>
-      <c r="E113" s="43"/>
-      <c r="F113" s="43"/>
-      <c r="G113" s="45"/>
-      <c r="H113" s="45"/>
-      <c r="I113" s="45"/>
-      <c r="J113" s="32"/>
-      <c r="K113" s="1"/>
-      <c r="L113" s="32"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="54"/>
+      <c r="E113" s="53"/>
+      <c r="F113" s="53"/>
+      <c r="G113" s="55"/>
+      <c r="H113" s="55"/>
+      <c r="I113" s="55"/>
+      <c r="J113" s="40"/>
+      <c r="K113" s="40"/>
+      <c r="L113" s="40"/>
       <c r="M113" s="1"/>
       <c r="N113" s="1"/>
       <c r="O113" s="1"/>
@@ -5429,17 +5663,17 @@
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1"/>
-      <c r="B114" s="42"/>
-      <c r="C114" s="43"/>
-      <c r="D114" s="44"/>
-      <c r="E114" s="43"/>
-      <c r="F114" s="43"/>
-      <c r="G114" s="45"/>
-      <c r="H114" s="45"/>
-      <c r="I114" s="45"/>
-      <c r="J114" s="32"/>
-      <c r="K114" s="1"/>
-      <c r="L114" s="32"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="53"/>
+      <c r="D114" s="54"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="53"/>
+      <c r="G114" s="55"/>
+      <c r="H114" s="55"/>
+      <c r="I114" s="55"/>
+      <c r="J114" s="40"/>
+      <c r="K114" s="40"/>
+      <c r="L114" s="40"/>
       <c r="M114" s="1"/>
       <c r="N114" s="1"/>
       <c r="O114" s="1"/>
@@ -26151,42 +26385,42 @@
       <c r="U1014" s="1"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="4" priority="1" stopIfTrue="1">
       <formula>$B8="Gerente de Projetos"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="5" priority="2" stopIfTrue="1">
       <formula>$B8="Membro Operacional"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="6" priority="3" stopIfTrue="1">
       <formula>$B8="Assessora de Vendas"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="6" priority="4" stopIfTrue="1">
       <formula>$B8="Assesora de Vendas"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="7" priority="5" stopIfTrue="1">
       <formula>$B8="Assessora Gestão de Pessoas 1"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="8" priority="6" stopIfTrue="1">
       <formula>$B8="Líder técnico de conhecimento"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="9" priority="7" stopIfTrue="1">
       <formula>$B8="tech_lead_projetos"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B8:J37">
+  <conditionalFormatting sqref="B8:J37 J40:J45">
     <cfRule type="expression" dxfId="10" priority="8" stopIfTrue="1">
       <formula>$B8="Assessora Gestão de Pessoas 2"</formula>
     </cfRule>
@@ -26218,218 +26452,218 @@
   <sheetData>
     <row r="1" ht="6.75" customHeight="1"/>
     <row r="2">
-      <c r="B2" s="46" t="s">
-        <v>88</v>
+      <c r="B2" s="56" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="47" t="s">
+      <c r="B3" s="57" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" s="47" t="s">
+      <c r="C3" s="57" t="s">
         <v>90</v>
       </c>
-      <c r="E3" s="47" t="s">
+      <c r="D3" s="57" t="s">
         <v>91</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="E3" s="57" t="s">
         <v>92</v>
       </c>
-      <c r="G3" s="47" t="s">
+      <c r="F3" s="57" t="s">
         <v>93</v>
       </c>
+      <c r="G3" s="57" t="s">
+        <v>94</v>
+      </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
-      <c r="B4" s="48" t="s">
-        <v>94</v>
-      </c>
-      <c r="C4" s="49" t="s">
+      <c r="B4" s="58" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="48">
+      <c r="C4" s="59" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="58">
         <v>4.0</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="58">
         <v>4.0</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="58">
         <v>4.0</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="60">
         <f t="shared" ref="G4:G9" si="1">IFERROR(AVERAGE(D4:F4),"")</f>
         <v>4</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="B5" s="51" t="s">
-        <v>96</v>
-      </c>
-      <c r="C5" s="49" t="s">
+      <c r="B5" s="61" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="48">
+      <c r="C5" s="59" t="s">
+        <v>98</v>
+      </c>
+      <c r="D5" s="58">
         <v>4.0</v>
       </c>
-      <c r="E5" s="48">
+      <c r="E5" s="58">
         <v>4.0</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="58">
         <v>4.0</v>
       </c>
-      <c r="G5" s="50">
+      <c r="G5" s="60">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
-      <c r="B6" s="51" t="s">
-        <v>98</v>
-      </c>
-      <c r="C6" s="49" t="s">
+      <c r="B6" s="61" t="s">
         <v>99</v>
       </c>
-      <c r="D6" s="48">
+      <c r="C6" s="59" t="s">
+        <v>100</v>
+      </c>
+      <c r="D6" s="58">
         <v>4.0</v>
       </c>
-      <c r="E6" s="48">
+      <c r="E6" s="58">
         <v>4.0</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="58">
         <v>4.0</v>
       </c>
-      <c r="G6" s="50">
+      <c r="G6" s="60">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
-      <c r="B7" s="51" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="49" t="s">
+      <c r="B7" s="61" t="s">
         <v>101</v>
       </c>
-      <c r="D7" s="48">
+      <c r="C7" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="58">
         <v>4.0</v>
       </c>
-      <c r="E7" s="48">
+      <c r="E7" s="58">
         <v>4.0</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="58">
         <v>4.0</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="60">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="B8" s="51" t="s">
-        <v>102</v>
-      </c>
-      <c r="C8" s="49" t="s">
+      <c r="B8" s="61" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="48">
+      <c r="C8" s="59" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="58">
         <v>4.0</v>
       </c>
-      <c r="E8" s="48">
+      <c r="E8" s="58">
         <v>4.0</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="58">
         <v>4.0</v>
       </c>
-      <c r="G8" s="50">
+      <c r="G8" s="60">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
-      <c r="B9" s="51" t="s">
+      <c r="B9" s="61" t="s">
         <v>18</v>
       </c>
-      <c r="C9" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="D9" s="48">
+      <c r="C9" s="59" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="58">
         <v>4.0</v>
       </c>
-      <c r="E9" s="48">
+      <c r="E9" s="58">
         <v>4.0</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="58">
         <v>4.0</v>
       </c>
-      <c r="G9" s="50">
+      <c r="G9" s="60">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
     </row>
     <row r="10" ht="15.75" customHeight="1">
-      <c r="C10" s="52"/>
+      <c r="C10" s="62"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
-      <c r="C11" s="52"/>
+      <c r="C11" s="62"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
-      <c r="C12" s="52"/>
+      <c r="C12" s="62"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="C13" s="52"/>
+      <c r="C13" s="62"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="C14" s="52"/>
+      <c r="C14" s="62"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="C15" s="52"/>
+      <c r="C15" s="62"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="C16" s="52"/>
+      <c r="C16" s="62"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="C17" s="52"/>
+      <c r="C17" s="62"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="C18" s="52"/>
+      <c r="C18" s="62"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="C19" s="52"/>
+      <c r="C19" s="62"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="C20" s="52"/>
+      <c r="C20" s="62"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="C21" s="52"/>
+      <c r="C21" s="62"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="C22" s="52"/>
+      <c r="C22" s="62"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="C23" s="52"/>
+      <c r="C23" s="62"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="C24" s="52"/>
+      <c r="C24" s="62"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="C25" s="52"/>
+      <c r="C25" s="62"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="C26" s="52"/>
+      <c r="C26" s="62"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="C27" s="52"/>
+      <c r="C27" s="62"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="52"/>
+      <c r="C28" s="62"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="52"/>
+      <c r="C29" s="62"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="52"/>
+      <c r="C30" s="62"/>
     </row>
   </sheetData>
   <dataValidations>
